--- a/para_equipe/nomes_dos_times.xlsx
+++ b/para_equipe/nomes_dos_times.xlsx
@@ -2,10 +2,6 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
   <sheets>
     <sheet name="Times" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
@@ -17,16 +13,28 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <color theme="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color theme="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -34,40 +42,46 @@
       <patternFill/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
+    <border/>
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -140,20 +154,20 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Sheets">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="4F81BD"/>
@@ -177,77 +191,19 @@
         <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="0000FF"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -259,166 +215,135 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -429,20 +354,20 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I69"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" style="7" min="1" max="1"/>
+    <col width="30" customWidth="1" style="7" min="2" max="2"/>
+    <col width="34" customWidth="1" style="7" min="3" max="3"/>
+    <col width="22" customWidth="1" style="7" min="4" max="4"/>
+    <col width="53.71" customWidth="1" style="7" min="5" max="5"/>
+    <col width="10" customWidth="1" style="7" min="6" max="6"/>
+    <col width="60" customWidth="1" style="7" min="7" max="8"/>
+    <col width="30" customWidth="1" style="7" min="9" max="9"/>
+    <col width="8.710000000000001" customWidth="1" style="7" min="10" max="26"/>
   </cols>
   <sheetData>
-    <row r="1" ht="45" customHeight="1">
+    <row r="1" ht="45" customHeight="1" s="7">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>slug (não editar)</t>
@@ -490,1978 +415,3502 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>ufmt_turuna</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>UFMT Turuna</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr"/>
-      <c r="D2" s="3" t="inlineStr"/>
-      <c r="E2" s="3" t="inlineStr"/>
-      <c r="F2" t="n">
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Turuna</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Universidade Federal de Mato Grosso</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>Rush Series Esquenta; Rush Series Esquenta 2; Univavá (Classificatória 1); Univavá (Classificatória 2); Univavá (Fase de Grupos)</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>ONEZERA 愛, balalov3, Kaytoh, fafa, ddz, duduziN</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr"/>
+      <c r="I2" s="5" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>azure_bears_black</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>Azure Bears Black</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" t="n">
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Azure B</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Universidade Tecnológica Federal do Paraná</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>Rush Series Esquenta; Rush Series Esquenta 2; Univavá (Classificatória 1); Univavá (Classificatória 2); Univavá (Classificatória 3); Univavá (Classificatória 4); Univavá (Fase de Grupos)</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>stockão, droga é o pedro, Lacerdaoo, Aldeath, Lacer, zeNith</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="I3" s="5" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>azure_bears_golden</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Azure Bears Golden</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr"/>
-      <c r="D4" s="3" t="inlineStr"/>
-      <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" t="n">
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Azure G</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Universidade Tecnológica Federal do Paraná</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>Rush Series Esquenta; Rush Series Esquenta 2; Univavá (Classificatória 1); Univavá (Fase de Grupos)</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>Kick, piM, greiN, andre, taek</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="I4" s="5" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>ceub_octopus_vulgaris</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>CEUB Octopus Vulgaris</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" t="n">
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Octopus V</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Centro Universitário de Brasília</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Rush Series Esquenta; Univavá (Classificatória 1); Univavá (Classificatória 2); Univavá (Classificatória 3); Univavá (Classificatória 4); Univavá (Fase de Grupos)</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>J3YP, Pockaus, tanizaki, nowAy, badaBIGBOSS, Dante</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="I5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>uscs_hawks</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>USCS Hawks</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" t="n">
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Hawks</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Universidade Municipal de São Caetano do Sul</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>Rush Series Esquenta; Rush Series Esquenta 2; Univavá (Classificatória 1); Univavá (Classificatória 2); Univavá (Classificatória 3); Univavá (Classificatória 4)</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>Cucinota, J5lidof, megan fox, Burckzs, blonded, ojapakashi</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="I6" s="5" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>totale_umc</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Totale UMC</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" t="n">
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Totale</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Universidade de Mogi das Cruzes</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>Rush Series Esquenta 2; Univavá (Classificatória 1); Univavá (Classificatória 3); Univavá (Fase de Grupos)</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>Dézinho, leoZinn, TOTALE Sephamm, pdrr, thzera33, 237</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="I7" s="5" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>fei_darkowls</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>FEI Darkowls</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" t="n">
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>FEI DarkOwls</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> DarkOwls</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Centro Universitário FEI</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>Rush Series Esquenta; Univavá (Classificatória 1); Univavá (Classificatória 2); Univavá (Classificatória 3); Univavá (Classificatória 4)</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>xerp, onizinnnnnn, Puosso, mεlo, lariø, oni666</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr"/>
+      <c r="I8" s="5" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>a2e_uff</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>A2E UFF</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" t="n">
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>A2E</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Universidade Federal Fluminense</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>Rush Series Esquenta; Univavá (Classificatória 1); Univavá (Classificatória 2); Univavá (Classificatória 3); Univavá (Classificatória 4)</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>tgzin, zuw, ninker, mth ツ, evatoj, daviZao</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="I9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>ufu_saints</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>UFU Saints</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr"/>
-      <c r="D10" s="3" t="inlineStr"/>
-      <c r="E10" s="3" t="inlineStr"/>
-      <c r="F10" t="n">
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Saints</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Universidade Federal de Uberlândia</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>Univavá (Classificatória 1); Univavá (Classificatória 2); Univavá (Fase de Grupos)</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>cks ヵ, marelo, Gutoso, Bellingham 10, oBigZe, obigzeh</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr"/>
+      <c r="I10" s="5" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>caap_hellhounds</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>CAAP Hellhounds</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="3" t="inlineStr"/>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" t="n">
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>CAAP H</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Universidade Federal do ABC</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>Univavá (Classificatória 1); Univavá (Classificatória 2); Univavá (Fase de Grupos)</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>CAAP Burrito42, CAAP Metal, CAAP medina, CAAP sobrunin, CAAP lopes, CAAP SUPERPDR1N</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr"/>
+      <c r="I11" s="5" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>ufpr_bbn</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>UFPR BBN</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr"/>
-      <c r="D12" s="3" t="inlineStr"/>
-      <c r="E12" s="3" t="inlineStr"/>
-      <c r="F12" t="n">
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Burning Bunnies UFPR</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Burn Bunn</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Universidade Federal do Paraná</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>Rush Series Esquenta; Univavá (Classificatória 1); Univavá (Classificatória 2); Univavá (Classificatória 3); Univavá (Classificatória 4)</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>BBN Tazyg, Lucky, BBN ishima, BBN Yuri, BBN wonDer, ZhiShou 执守</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr"/>
+      <c r="I12" s="5" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>wolf_gaming</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>Wolf Gaming</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr"/>
-      <c r="D13" s="3" t="inlineStr"/>
-      <c r="E13" s="3" t="inlineStr"/>
-      <c r="F13" t="n">
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Wolf</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Universidade Federal de Ciência e Inovação do Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>Univavá (Classificatória 1); Univavá (Fase de Grupos)</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>bielmonster, nizk, spx, salem, dark, tay</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr"/>
+      <c r="I13" s="5" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>inatel_legacy</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Inatel Legacy</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr"/>
-      <c r="D14" s="3" t="inlineStr"/>
-      <c r="E14" s="3" t="inlineStr"/>
-      <c r="F14" t="n">
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Inatel L</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Instituto Nacional de Telecomunicações</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>Rush Series Esquenta; Univavá (Classificatória 1); Univavá (Classificatória 2); Univavá (Classificatória 3)</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>Novinhu, INTL Psychovv, psч, Mtr, Bebelzinh0, Izanagi</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr"/>
+      <c r="I14" s="5" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>minerva_thunders</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Minerva Thunders</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="3" t="inlineStr"/>
-      <c r="E15" s="3" t="inlineStr"/>
-      <c r="F15" t="n">
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Minerva T</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Universidade Federal do Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>Univavá (Classificatória 3); Univavá (Fase de Grupos)</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>thenker, Freec, schroud 7wzz, mtch L, Stalkzin, swpz</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr"/>
+      <c r="I15" s="5" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>maua_blue</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>Mauá Blue</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="3" t="inlineStr"/>
-      <c r="E16" s="3" t="inlineStr"/>
-      <c r="F16" t="n">
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Mauá B</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Instituto Mauá de Tecnologia</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>Univavá (Classificatória 2); Univavá (Classificatória 3); Univavá (Classificatória 4)</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>IMT krownnl, kikito, IMT Greed, miglin capudo, Pipão, IMT prime</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr"/>
+      <c r="I16" s="5" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>axis_anteaters</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>Axis Anteaters</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="3" t="inlineStr"/>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" t="n">
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Universidade Federal do ABC</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>Univavá (Classificatória 2); Univavá (Fase de Grupos)</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>Duduka, Luqueta, Zé Drops, vladi, dnkzao, larpginger</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr"/>
+      <c r="I17" s="5" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>caap_auroras</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>CAAP Auroras</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr"/>
-      <c r="D18" s="3" t="inlineStr"/>
-      <c r="E18" s="3" t="inlineStr"/>
-      <c r="F18" t="n">
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>CAAP A</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Universidade Federal do ABC</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>Rush Series Esquenta; Rush Series Inclusivo; Univavá (Classificatória 2); Univavá (Classificatória 4)</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>sopas, CAAP AnaGi, Hoopa, mist, Mimikyu, CAAP Meowolet</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr"/>
+      <c r="I18" s="5" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>fei_whiteowls</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>FEI Whiteowls</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr"/>
-      <c r="D19" s="3" t="inlineStr"/>
-      <c r="E19" s="3" t="inlineStr"/>
-      <c r="F19" t="n">
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>WhiteOwl</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Centro Universitário FEI</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>Rush Series Esquenta; Univavá (Classificatória 1); Univavá (Classificatória 3); Univavá (Classificatória 4)</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>motta, fxz nightmare, Puosso, bogao, KamiKazeee, fxz não choraxx</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr"/>
+      <c r="I19" s="5" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>octacore_python</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Octacore Python</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr"/>
-      <c r="D20" s="3" t="inlineStr"/>
-      <c r="E20" s="3" t="inlineStr"/>
-      <c r="F20" t="n">
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Octa Pyth</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Pontifícia Universidade Católica do Paraná</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>Rush Series Esquenta 2; Univavá (Classificatória 1); Univavá (Classificatória 2)</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>Phioe, TUK, floquinho67, Tonho, near, haku</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="I20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1" s="7">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>green_owls_jacurutu</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>Green Owls Jacurutu</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" t="n">
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>GO Jacuru</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Universidade de Brasília</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>Univavá (Classificatória 4); Univavá (Fase de Grupos)</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>Noya, cavaloanão, konnZ, AIM Yasuzinn ツ, Lisa, mistakeZ</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="I21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1" s="7">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>unicamp_tritons_black</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>Unicamp Tritons Black</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr"/>
-      <c r="D22" s="3" t="inlineStr"/>
-      <c r="E22" s="3" t="inlineStr"/>
-      <c r="F22" t="n">
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Tritons B</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Universidade Estadual de Campinas</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>Rush Series Esquenta; Univavá (Classificatória 2); Univavá (Classificatória 3); Univavá (Classificatória 4)</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>Whatsapp, llenn, makola, Driblas, TTS Mv, pivA</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="I22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" s="7">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>pucc_cardinals</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>PUC-Campinas Cardinals</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="3" t="inlineStr"/>
-      <c r="F23" t="n">
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Cardinal</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Pontifícia Universidade Católica de Campinas</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>Univavá (Classificatória 1); Univavá (Classificatória 2); Univavá (Classificatória 4)</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>é o maldito, apo, PUCC Hasp, PUCC ttt, PUCC maumauxdd1, fr0st</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="I23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="15.75" customHeight="1" s="7">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>furia_utfpr</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Furia UTFPR</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr"/>
-      <c r="D24" s="3" t="inlineStr"/>
-      <c r="E24" s="3" t="inlineStr"/>
-      <c r="F24" t="n">
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Furia</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Universidade Tecnológica Federal do Paraná</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>Univavá (Classificatória 3); Univavá (Fase de Grupos)</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>kssarato, AsianJack, Veterano, GabrielH, krozz</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="I24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1" s="7">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>green_owls_noctua</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>Green Owls Noctua</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr"/>
-      <c r="D25" s="3" t="inlineStr"/>
-      <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" t="n">
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>GO Noctua</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Universidade de Brasília</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>Univavá (Classificatória 2); Univavá (Classificatória 3); Univavá (Fase de Grupos)</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H25" s="6" t="inlineStr">
         <is>
           <t>Straw, tequila, Piubelli, JoSueLanches, otts, Verno sem mira</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="I25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1" s="7">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>caap_malditos</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>CAAP Malditos</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr"/>
-      <c r="D26" s="3" t="inlineStr"/>
-      <c r="E26" s="3" t="inlineStr"/>
-      <c r="F26" t="n">
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>CAAP Ma</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Universidade Federal do ABC</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>Univavá (Classificatória 3); Univavá (Classificatória 4)</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="6" t="inlineStr">
         <is>
           <t>Doragon, mist, CAAP protanzy42, anp4, meno kabrinha, duarteskz</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="I26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1" s="7">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>macklogic_red</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>Macklogic Red</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="3" t="inlineStr"/>
-      <c r="E27" s="3" t="inlineStr"/>
-      <c r="F27" t="n">
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>MackLogic RED</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Mack Red</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Universidade Presbiteriana Mackenzie</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>Univavá (Classificatória 1); Univavá (Fase de Grupos)</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>sick, Katojin, lule, gubert 水, Eu sou o Choco, Kato</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="I27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="15.75" customHeight="1" s="7">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>usp_stars</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>USP Stars</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="3" t="inlineStr"/>
-      <c r="E28" s="3" t="inlineStr"/>
-      <c r="F28" t="n">
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Stars</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Universidade de São Paulo</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>Univavá (Classificatória 4); Univavá (Fase de Grupos)</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H28" s="6" t="inlineStr">
         <is>
           <t>Rype, GalloBill, yuta okkotsu, quero um arduino, Dioguera, GPTTERAPIAAPOIA</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="I28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1" s="7">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>poli_plague</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>Poli Plague</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="3" t="inlineStr"/>
-      <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" t="n">
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Poli</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Universidade de São Paulo</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>Univavá (Classificatória 1); Univavá (Classificatória 2); Univavá (Classificatória 3); Univavá (Classificatória 4)</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H29" s="6" t="inlineStr">
         <is>
           <t>Vks, littlecyber, LoveHatsuneMiku, Lukako, ruidow, Osíris</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="I29" s="5" t="n"/>
+    </row>
+    <row r="30" ht="15.75" customHeight="1" s="7">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>inatel</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>Inatel</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr"/>
-      <c r="D30" s="3" t="inlineStr"/>
-      <c r="E30" s="3" t="inlineStr"/>
-      <c r="F30" t="n">
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Inatel</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Instituto Nacional de Telecomunicações</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" s="6" t="inlineStr">
         <is>
           <t>Rush Series Esquenta 2; Univavá (Classificatória 3); Univavá (Classificatória 4)</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H30" s="6" t="inlineStr">
         <is>
           <t>NicotiNaa, INTL DaviPsadelo, 乙ordaИ   乡, 疲れた, Kauan, dan 光环</t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="I30" s="5" t="n"/>
+    </row>
+    <row r="31" ht="15.75" customHeight="1" s="7">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>ceub_octopus</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>CEUB Octopus</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="3" t="inlineStr"/>
-      <c r="E31" s="3" t="inlineStr"/>
-      <c r="F31" t="n">
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Octopus</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Centro Universitário de Brasília</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" s="6" t="inlineStr">
         <is>
           <t>Univavá (Classificatória 1); Univavá (Fase de Grupos)</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H31" s="6" t="inlineStr">
         <is>
           <t>seki, chadu, reyblock, kzr, big0d, JotaVe</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="I31" s="5" t="n"/>
+    </row>
+    <row r="32" ht="15.75" customHeight="1" s="7">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>pucgo_sistematica</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>PUC-GO Sistematica</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr"/>
-      <c r="D32" s="3" t="inlineStr"/>
-      <c r="E32" s="3" t="inlineStr"/>
-      <c r="F32" t="n">
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Pontifícia Universidade Católica de Goiás</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="6" t="inlineStr">
         <is>
           <t>Univavá (Classificatória 3); Univavá (Classificatória 4)</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H32" s="6" t="inlineStr">
         <is>
           <t>darkzin 影, Não é o Gui krl, Lzおあ, lou, DiZinOnFire, demon lz</t>
         </is>
       </c>
-      <c r="I32" s="3" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="I32" s="5" t="n"/>
+    </row>
+    <row r="33" ht="15.75" customHeight="1" s="7">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>inatel_gray</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>Inatel Gray</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="3" t="inlineStr"/>
-      <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" t="n">
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Inatel G</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Instituto Nacional de Telecomunicações</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="6" t="inlineStr">
         <is>
           <t>Rush Series Esquenta 2; Rush Series Inclusivo; Univavá (Classificatória 2); Univavá (Classificatória 4)</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H33" s="6" t="inlineStr">
         <is>
           <t>INTL chica, INTL Juh, INTL mile, INTL tambaqui, INTL kyria, lost</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="I33" s="5" t="n"/>
+    </row>
+    <row r="34" ht="15.75" customHeight="1" s="7">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>caap_momentum</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>CAAP Momentum</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr"/>
-      <c r="D34" s="3" t="inlineStr"/>
-      <c r="E34" s="3" t="inlineStr"/>
-      <c r="F34" t="n">
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>CAAP Mo</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Universidade Federal do ABC</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="6" t="inlineStr">
         <is>
           <t>Univavá (Classificatória 1); Univavá (Classificatória 2)</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H34" s="6" t="inlineStr">
         <is>
           <t>ric, klouzz, duarteskz, anzy, superpdr1n, CAAP SUPERPDR1N</t>
         </is>
       </c>
-      <c r="I34" s="3" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="I34" s="5" t="n"/>
+    </row>
+    <row r="35" ht="15.75" customHeight="1" s="7">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>inatel_dois</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>Inatel Dois</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr"/>
-      <c r="D35" s="3" t="inlineStr"/>
-      <c r="E35" s="3" t="inlineStr"/>
-      <c r="F35" t="n">
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Inatel Black</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Inatel B</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Instituto Nacional de Telecomunicações</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" s="6" t="inlineStr">
         <is>
           <t>Univavá (Classificatória 2); Univavá (Classificatória 3); Univavá (Classificatória 4)</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H35" s="6" t="inlineStr">
         <is>
           <t>JGRB, TotyZ, sane, Nero, 12 ama o galo, twelve will win</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="I35" s="5" t="n"/>
+    </row>
+    <row r="36" ht="15.75" customHeight="1" s="7">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>ufmg_fenix_b</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>UFMG Fênix B</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr"/>
-      <c r="D36" s="3" t="inlineStr"/>
-      <c r="E36" s="3" t="inlineStr"/>
-      <c r="F36" t="n">
+      <c r="C36" s="5" t="n"/>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Fênix</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Universidade Federal de Minas Gerais</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" s="6" t="inlineStr">
         <is>
           <t>Univavá (Classificatória 1); Univavá (Classificatória 3); Univavá (Classificatória 4)</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H36" s="6" t="inlineStr">
         <is>
           <t>Cientista, MacMolho, Kamachow, Sunny, Indra The Runner, Sai</t>
         </is>
       </c>
-      <c r="I36" s="3" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="I36" s="5" t="n"/>
+    </row>
+    <row r="37" ht="15.75" customHeight="1" s="7">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>liga_vulkanica</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>Liga Vulkanica</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr"/>
-      <c r="D37" s="3" t="inlineStr"/>
-      <c r="E37" s="3" t="inlineStr"/>
-      <c r="F37" t="n">
+      <c r="C37" s="5" t="n"/>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Vulkanic</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Universidade do Estado de Mato Grosso </t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" s="6" t="inlineStr">
         <is>
           <t>Univavá (Classificatória 2); Univavá (Classificatória 3); Univavá (Classificatória 4)</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H37" s="6" t="inlineStr">
         <is>
           <t>LHC JF, Mateuspa, BK 47, Lowyu, SloW aim, the demon bird</t>
         </is>
       </c>
-      <c r="I37" s="3" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="I37" s="5" t="n"/>
+    </row>
+    <row r="38" ht="15.75" customHeight="1" s="7">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>azure_bears_silver</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>Azure Bears Silver</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr"/>
-      <c r="D38" s="3" t="inlineStr"/>
-      <c r="E38" s="3" t="inlineStr"/>
-      <c r="F38" t="n">
+      <c r="C38" s="5" t="n"/>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Azure S</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>Universidade Tecnológica Federal do Paraná</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G38" s="6" t="inlineStr">
         <is>
           <t>Univavá (Classificatória 1); Univavá (Classificatória 3); Univavá (Classificatória 4)</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H38" s="6" t="inlineStr">
         <is>
           <t>ÔMEGA 9x90, dvd isnt perfect, Andronicca, s kd, khianh, Rapunzel</t>
         </is>
       </c>
-      <c r="I38" s="3" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="I38" s="5" t="n"/>
+    </row>
+    <row r="39" ht="15.75" customHeight="1" s="7">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>unifesp_erex</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>UNIFESP EREX</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr"/>
-      <c r="D39" s="3" t="inlineStr"/>
-      <c r="E39" s="3" t="inlineStr"/>
-      <c r="F39" t="n">
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>UNIFESP E-REX</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>E-REX</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Universidade Federal de São Paulo</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="6" t="inlineStr">
         <is>
           <t>Univavá (Classificatória 1); Univavá (Classificatória 3); Univavá (Classificatória 4)</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H39" s="6" t="inlineStr">
         <is>
           <t>Flangø, VELOSO, Lica, pai, jordan, EUDISPARADO</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="I39" s="5" t="n"/>
+    </row>
+    <row r="40" ht="15.75" customHeight="1" s="7">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>macklogic_rainbow</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>Macklogic Rainbow</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr"/>
-      <c r="D40" s="3" t="inlineStr"/>
-      <c r="E40" s="3" t="inlineStr"/>
-      <c r="F40" t="n">
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>MackLogic Rainbow</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Mack Rain</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>Universidade Presbiteriana Mackenzie</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G40" s="6" t="inlineStr">
         <is>
           <t>Rush Series Esquenta 2; Rush Series Inclusivo</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H40" s="6" t="inlineStr">
         <is>
           <t>Jubz 山, Sloretti, instinct, lule, yonaha 山, malagueta</t>
         </is>
       </c>
-      <c r="I40" s="3" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="I40" s="5" t="n"/>
+    </row>
+    <row r="41" ht="15.75" customHeight="1" s="7">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>fatec_pg</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>FATEC PG</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr"/>
-      <c r="D41" s="3" t="inlineStr"/>
-      <c r="E41" s="3" t="inlineStr"/>
-      <c r="F41" t="n">
+      <c r="C41" s="5" t="n"/>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Faculdade de Tecnologia de São Paulo</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>Rush Series Esquenta 2; Univavá (Classificatória 4)</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H41" s="6" t="inlineStr">
         <is>
           <t>n0isy 성, Artzz XD, katori, shisui, TTV paivaz01, Liquid Amon</t>
         </is>
       </c>
-      <c r="I41" s="3" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="I41" s="5" t="n"/>
+    </row>
+    <row r="42" ht="15.75" customHeight="1" s="7">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>ufu_saints_auryn</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>UFU Saints Auryn</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr"/>
-      <c r="D42" s="3" t="inlineStr"/>
-      <c r="E42" s="3" t="inlineStr"/>
-      <c r="F42" t="n">
+      <c r="C42" s="5" t="n"/>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Saints A</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>Universidade Federal de Uberlândia</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G42" s="6" t="inlineStr">
         <is>
           <t>Rush Series Esquenta; Rush Series Inclusivo</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H42" s="6" t="inlineStr">
         <is>
           <t>chamuska, FFS candeLARIa, fronk, juju engenheira, Siren, jettlag</t>
         </is>
       </c>
-      <c r="I42" s="3" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="I42" s="5" t="n"/>
+    </row>
+    <row r="43" ht="15.75" customHeight="1" s="7">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>unicamp_tritons_red</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>Unicamp Tritons Red</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr"/>
-      <c r="D43" s="3" t="inlineStr"/>
-      <c r="E43" s="3" t="inlineStr"/>
-      <c r="F43" t="n">
+      <c r="C43" s="5" t="n"/>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Tritons R</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Universidade Estadual de Campinas</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G43" s="6" t="inlineStr">
         <is>
           <t>Rush Series Esquenta 2; Univavá (Classificatória 1)</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H43" s="6" t="inlineStr">
         <is>
           <t>drs1 rei de itu, BRaim, goavyy, makola, É O TAL DO MV</t>
         </is>
       </c>
-      <c r="I43" s="3" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="I43" s="5" t="n"/>
+    </row>
+    <row r="44" ht="15.75" customHeight="1" s="7">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>pucgo_sistematica_academy</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>PUC-GO Sistematica Academy</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr"/>
-      <c r="D44" s="3" t="inlineStr"/>
-      <c r="E44" s="3" t="inlineStr"/>
-      <c r="F44" t="n">
+      <c r="C44" s="5" t="n"/>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Sistema A</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>Pontifícia Universidade Católica de Goiás</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G44" s="6" t="inlineStr">
         <is>
           <t>Univavá (Classificatória 1); Univavá (Classificatória 3); Univavá (Classificatória 4)</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H44" s="6" t="inlineStr">
         <is>
           <t>nonimo, Dunstere, Victhos, zwei, DAYBREAK, Rudini</t>
         </is>
       </c>
-      <c r="I44" s="3" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="I44" s="5" t="n"/>
+    </row>
+    <row r="45" ht="15.75" customHeight="1" s="7">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>octacore_javascript</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>Octacore Javascript</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="3" t="inlineStr"/>
-      <c r="E45" s="3" t="inlineStr"/>
-      <c r="F45" t="n">
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Octacore Java Script</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Octa Java</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Pontifícia Universidade Católica do Paraná</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G45" s="6" t="inlineStr">
         <is>
           <t>Rush Series Esquenta; Rush Series Esquenta 2; Univavá (Classificatória 1)</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H45" s="6" t="inlineStr">
         <is>
           <t>gyukaa, Soulless, Zé Leão, S E Y P H A, KNZ, Ice</t>
         </is>
       </c>
-      <c r="I45" s="3" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="I45" s="5" t="n"/>
+    </row>
+    <row r="46" ht="15.75" customHeight="1" s="7">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>ufg_eagles_blue</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>UFG Eagles Blue</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr"/>
-      <c r="D46" s="3" t="inlineStr"/>
-      <c r="E46" s="3" t="inlineStr"/>
-      <c r="F46" t="n">
+      <c r="C46" s="5" t="n"/>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Eagles B</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>Universidade Federal de Goiás</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G46" s="6" t="inlineStr">
         <is>
           <t>Univavá (Classificatória 1); Univavá (Classificatória 3)</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H46" s="6" t="inlineStr">
         <is>
           <t>Fabdgno, yFreakks2, llucky, KADDES, we cry together, artsi</t>
         </is>
       </c>
-      <c r="I46" s="3" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="I46" s="5" t="n"/>
+    </row>
+    <row r="47" ht="15.75" customHeight="1" s="7">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>fametro_berserkers</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>FAMETRO Berserkers</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr"/>
-      <c r="D47" s="3" t="inlineStr"/>
-      <c r="E47" s="3" t="inlineStr"/>
-      <c r="F47" t="n">
+      <c r="C47" s="5" t="n"/>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Berserke</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Centro Universitário Fametro</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G47" s="6" t="inlineStr">
         <is>
           <t>Univavá (Classificatória 4)</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H47" s="6" t="inlineStr">
         <is>
           <t>mrn777, Targ1no 神, suino, neguzera69, mindos 22, MRK</t>
         </is>
       </c>
-      <c r="I47" s="3" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="I47" s="5" t="n"/>
+    </row>
+    <row r="48" ht="15.75" customHeight="1" s="7">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>macklogic_white</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>Macklogic White</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr"/>
-      <c r="D48" s="3" t="inlineStr"/>
-      <c r="E48" s="3" t="inlineStr"/>
-      <c r="F48" t="n">
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>MackLogic White</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Mack Whit</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>Universidade Presbiteriana Mackenzie</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G48" s="6" t="inlineStr">
         <is>
           <t>Univavá (Classificatória 1); Univavá (Classificatória 4)</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H48" s="6" t="inlineStr">
         <is>
           <t>sqrtl peek, Elden, Jungkook, Foca Não, zezinhoDasPARTY, Lodon6</t>
         </is>
       </c>
-      <c r="I48" s="3" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="I48" s="5" t="n"/>
+    </row>
+    <row r="49" ht="15.75" customHeight="1" s="7">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>ufg_eagles</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>UFG Eagles</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr"/>
-      <c r="D49" s="3" t="inlineStr"/>
-      <c r="E49" s="3" t="inlineStr"/>
-      <c r="F49" t="n">
+      <c r="C49" s="5" t="n"/>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Eagles</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Universidade Federal de Goiás</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G49" s="6" t="inlineStr">
         <is>
           <t>Univavá (Classificatória 1)</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H49" s="6" t="inlineStr">
         <is>
           <t>CVN, docas culture, darnubra, raap, reh</t>
         </is>
       </c>
-      <c r="I49" s="3" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="I49" s="5" t="n"/>
+    </row>
+    <row r="50" ht="15.75" customHeight="1" s="7">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>gambiarra_ufg</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>Gambiarra UFG</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr"/>
-      <c r="D50" s="3" t="inlineStr"/>
-      <c r="E50" s="3" t="inlineStr"/>
-      <c r="F50" t="n">
+      <c r="C50" s="5" t="n"/>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>Gambi</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>Universidade Federal de Goiás</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G50" s="6" t="inlineStr">
         <is>
           <t>Univavá (Classificatória 4)</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H50" s="6" t="inlineStr">
         <is>
           <t>a3e3 Kurts, Kebi Láo, Br0sツ, suco de gesso 2, balao</t>
         </is>
       </c>
-      <c r="I50" s="3" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="I50" s="5" t="n"/>
+    </row>
+    <row r="51" ht="15.75" customHeight="1" s="7">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>brutal_esports</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>Brutal Esports</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr"/>
-      <c r="D51" s="3" t="inlineStr"/>
-      <c r="E51" s="3" t="inlineStr"/>
-      <c r="F51" t="n">
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Brutal eSports</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Brutal</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Universidade Federal de São João del-Rei</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G51" s="6" t="inlineStr">
         <is>
           <t>Univavá (Classificatória 4)</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H51" s="6" t="inlineStr">
         <is>
           <t>Lozartan, aiko, Dirt, bmo, nw 友</t>
         </is>
       </c>
-      <c r="I51" s="3" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="I51" s="5" t="n"/>
+    </row>
+    <row r="52" ht="15.75" customHeight="1" s="7">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>ibmec_sharks</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>Ibmec Sharks</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr"/>
-      <c r="D52" s="3" t="inlineStr"/>
-      <c r="E52" s="3" t="inlineStr"/>
-      <c r="F52" t="n">
+      <c r="C52" s="5" t="n"/>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Sharks</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>Instituto Brasileiro de Mercado de Capitais</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G52" s="6" t="inlineStr">
         <is>
           <t>Rush Series Esquenta 2</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H52" s="6" t="inlineStr">
         <is>
           <t>Jannuzz1, Mith, deiv the kid, LKzin, nao estou xitado</t>
         </is>
       </c>
-      <c r="I52" s="3" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="I52" s="5" t="n"/>
+    </row>
+    <row r="53" ht="15.75" customHeight="1" s="7">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>ime_wolves_red</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>IME Wolves Red</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr"/>
-      <c r="D53" s="3" t="inlineStr"/>
-      <c r="E53" s="3" t="inlineStr"/>
-      <c r="F53" t="n">
+      <c r="C53" s="5" t="n"/>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Wolves R</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>Instituto Militar de Engenharia</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G53" s="6" t="inlineStr">
         <is>
           <t>Rush Series Esquenta; Univavá (Classificatória 2)</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H53" s="6" t="inlineStr">
         <is>
           <t>taverz, katsuchi, kharuy, kiwi, Elph Tcanmar, Ayslan loves L</t>
         </is>
       </c>
-      <c r="I53" s="3" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="I53" s="5" t="n"/>
+    </row>
+    <row r="54" ht="15.75" customHeight="1" s="7">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>panterao_gaming</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>Panterão Gaming</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr"/>
-      <c r="D54" s="3" t="inlineStr"/>
-      <c r="E54" s="3" t="inlineStr"/>
-      <c r="F54" t="n">
+      <c r="C54" s="5" t="n"/>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Panterão</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>Universidade Federal de Ciência e Inovação de Minas Gerais</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G54" s="6" t="inlineStr">
         <is>
           <t>Rush Series Esquenta 2; Univavá (Classificatória 4)</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H54" s="6" t="inlineStr">
         <is>
           <t>Didado, ESCkey, Vani, tcguedess, Teuzyn o editor, Teuzyn</t>
         </is>
       </c>
-      <c r="I54" s="3" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="I54" s="5" t="n"/>
+    </row>
+    <row r="55" ht="15.75" customHeight="1" s="7">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>axis_aura</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>Axis Aura</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr"/>
-      <c r="D55" s="3" t="inlineStr"/>
-      <c r="E55" s="3" t="inlineStr"/>
-      <c r="F55" t="n">
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Axis Anteaters - Aura</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Axis Aura</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>Universidade Federal do ABC</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G55" s="6" t="inlineStr">
         <is>
           <t>Univavá (Classificatória 1)</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H55" s="6" t="inlineStr">
         <is>
           <t>Duduka, Calangod, Madrini, Nightrise, ySantosz</t>
         </is>
       </c>
-      <c r="I55" s="3" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="I55" s="5" t="n"/>
+    </row>
+    <row r="56" ht="15.75" customHeight="1" s="7">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>azure_bears_white</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>Azure Bears White</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr"/>
-      <c r="D56" s="3" t="inlineStr"/>
-      <c r="E56" s="3" t="inlineStr"/>
-      <c r="F56" t="n">
+      <c r="C56" s="5" t="n"/>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>Azure W</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>Universidade Tecnológica Federal do Paraná</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G56" s="6" t="inlineStr">
         <is>
           <t>Rush Series Inclusivo</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H56" s="6" t="inlineStr">
         <is>
           <t>Maki Zenin 全員, ScherBi, Andronicca, moonッ, trix</t>
         </is>
       </c>
-      <c r="I56" s="3" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="I56" s="5" t="n"/>
+    </row>
+    <row r="57" ht="15.75" customHeight="1" s="7">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>tigre_branco</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="6" t="inlineStr">
         <is>
           <t>Tigre Branco</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr"/>
-      <c r="D57" s="3" t="inlineStr"/>
-      <c r="E57" s="3" t="inlineStr"/>
-      <c r="F57" t="n">
+      <c r="C57" s="5" t="n"/>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Tigre</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Faculdade Donaduzz</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G57" s="6" t="inlineStr">
         <is>
           <t>Rush Series Esquenta</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H57" s="6" t="inlineStr">
         <is>
           <t>Brandão, nataN, z1n, World Hold on, Th7, Gutp</t>
         </is>
       </c>
-      <c r="I57" s="3" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="I57" s="5" t="n"/>
+    </row>
+    <row r="58" ht="15.75" customHeight="1" s="7">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>ufu_saints_trigons</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>UFU Saints Trigons</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr"/>
-      <c r="D58" s="3" t="inlineStr"/>
-      <c r="E58" s="3" t="inlineStr"/>
-      <c r="F58" t="n">
+      <c r="C58" s="5" t="n"/>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>Saints T</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>Universidade Federal de Uberlândia</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G58" s="6" t="inlineStr">
         <is>
           <t>Univavá (Classificatória 4)</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H58" s="6" t="inlineStr">
         <is>
           <t>Athos778, ppeuz, warplane, trashzerra, lovers rock</t>
         </is>
       </c>
-      <c r="I58" s="3" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="I58" s="5" t="n"/>
+    </row>
+    <row r="59" ht="15.75" customHeight="1" s="7">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>ufrj_minerva</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="6" t="inlineStr">
         <is>
           <t>UFRJ Minerva</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr"/>
-      <c r="D59" s="3" t="inlineStr"/>
-      <c r="E59" s="3" t="inlineStr"/>
-      <c r="F59" t="n">
+      <c r="C59" s="5" t="n"/>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Minerva</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>Universidade Federal do Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G59" s="6" t="inlineStr">
         <is>
           <t>Univavá (Classificatória 4)</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="H59" s="6" t="inlineStr">
         <is>
           <t>loverman, ブレンノ, BBL lovers rock, DG  叶, Kozolove</t>
         </is>
       </c>
-      <c r="I59" s="3" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="I59" s="5" t="n"/>
+    </row>
+    <row r="60" ht="15.75" customHeight="1" s="7">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>usp_stars_gc</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>USP Stars GC</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr"/>
-      <c r="D60" s="3" t="inlineStr"/>
-      <c r="E60" s="3" t="inlineStr"/>
-      <c r="F60" t="n">
+      <c r="C60" s="5" t="n"/>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>Stars GC</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>Universidade de São Paulo</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G60" s="6" t="inlineStr">
         <is>
           <t>Rush Series Inclusivo</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="H60" s="6" t="inlineStr">
         <is>
           <t>Kelvin, thaly, misstressa, kharuy, Ndmi</t>
         </is>
       </c>
-      <c r="I60" s="3" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="I60" s="5" t="n"/>
+    </row>
+    <row r="61" ht="15.75" customHeight="1" s="7">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>homem_passaro</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="6" t="inlineStr">
         <is>
           <t>Homem Passaro</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr"/>
-      <c r="D61" s="3" t="inlineStr"/>
-      <c r="E61" s="3" t="inlineStr"/>
-      <c r="F61" t="n">
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>Homem Pássaro</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>H Pássaro</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>Faculdade Cásper Líbero</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G61" s="6" t="inlineStr">
         <is>
           <t>Univavá (Classificatória 1)</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="H61" s="6" t="inlineStr">
         <is>
           <t>letz, dybala 021, dexter morgan, stit, washed</t>
         </is>
       </c>
-      <c r="I61" s="3" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="I61" s="5" t="n"/>
+    </row>
+    <row r="62" ht="15.75" customHeight="1" s="7">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>ufg_gc_eagles</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="6" t="inlineStr">
         <is>
           <t>UFG GC Eagles</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr"/>
-      <c r="D62" s="3" t="inlineStr"/>
-      <c r="E62" s="3" t="inlineStr"/>
-      <c r="F62" t="n">
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>UFG Eagles GC</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>Eagles GC</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>Universidade Federal de Goiás</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G62" s="6" t="inlineStr">
         <is>
           <t>Univavá (Classificatória 1)</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="H62" s="6" t="inlineStr">
         <is>
           <t>CherryX, clara em neve, Pferes, ajaxy, VuiCiK, akzinha</t>
         </is>
       </c>
-      <c r="I62" s="3" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="I62" s="5" t="n"/>
+    </row>
+    <row r="63" ht="15.75" customHeight="1" s="7">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>pucc_canaries</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="6" t="inlineStr">
         <is>
           <t>PUC-Campinas Canaries</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr"/>
-      <c r="D63" s="3" t="inlineStr"/>
-      <c r="E63" s="3" t="inlineStr"/>
-      <c r="F63" t="n">
+      <c r="C63" s="5" t="n"/>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Canaries</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Pontifícia Universidade Católica de Campinas</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G63" s="6" t="inlineStr">
         <is>
           <t>Rush Series Inclusivo</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H63" s="6" t="inlineStr">
         <is>
           <t>madu, honeymoon, Crystallinee, raye, MMZ Larissinha, azitromicina</t>
         </is>
       </c>
-      <c r="I63" s="3" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="I63" s="5" t="n"/>
+    </row>
+    <row r="64" ht="15.75" customHeight="1" s="7">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>unirio_krakens</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="6" t="inlineStr">
         <is>
           <t>UNIRIO Krakens</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr"/>
-      <c r="D64" s="3" t="inlineStr"/>
-      <c r="E64" s="3" t="inlineStr"/>
-      <c r="F64" t="n">
+      <c r="C64" s="5" t="n"/>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>Krakens</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>Universidade Federal do Estado do Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G64" s="6" t="inlineStr">
         <is>
           <t>Univavá (Classificatória 4)</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="H64" s="6" t="inlineStr">
         <is>
           <t>KRK Lucky, KRK LT, KRK 天鎖斬月, KRK Camlui12, KRK сатюяо</t>
         </is>
       </c>
-      <c r="I64" s="3" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="I64" s="5" t="n"/>
+    </row>
+    <row r="65" ht="15.75" customHeight="1" s="7">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>gdu_ufpb</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="6" t="inlineStr">
         <is>
           <t>GDU UFPB</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr"/>
-      <c r="D65" s="3" t="inlineStr"/>
-      <c r="E65" s="3" t="inlineStr"/>
-      <c r="F65" t="n">
+      <c r="C65" s="5" t="n"/>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>GDU</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>Universidade Federal da Paraíba</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G65" s="6" t="inlineStr">
         <is>
           <t>Univavá (Classificatória 1)</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="H65" s="6" t="inlineStr">
         <is>
           <t>romedes, Bad Rez, Xing RAX, MEU IOIÔ, šŁg シ</t>
         </is>
       </c>
-      <c r="I65" s="3" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="I65" s="5" t="n"/>
+    </row>
+    <row r="66" ht="15.75" customHeight="1" s="7">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>sheriff_iff</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="6" t="inlineStr">
         <is>
           <t>Sheriff IFF</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr"/>
-      <c r="D66" s="3" t="inlineStr"/>
-      <c r="E66" s="3" t="inlineStr"/>
-      <c r="F66" t="n">
+      <c r="C66" s="5" t="n"/>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>Sheriff</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>Instituto Federal Fluminense</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G66" s="6" t="inlineStr">
         <is>
           <t>Univavá (Classificatória 4)</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="H66" s="6" t="inlineStr">
         <is>
           <t>aQc, rahg, Eraj, Fael, lucKZin</t>
         </is>
       </c>
-      <c r="I66" s="3" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="I66" s="5" t="n"/>
+    </row>
+    <row r="67" ht="15.75" customHeight="1" s="7">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>rahnag</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="6" t="inlineStr">
         <is>
           <t>Rahnag</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr"/>
-      <c r="D67" s="3" t="inlineStr"/>
-      <c r="E67" s="3" t="inlineStr"/>
-      <c r="F67" t="n">
+      <c r="C67" s="5" t="n"/>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Rahnag</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>Centro Universitário do Distrito Federal</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G67" s="6" t="inlineStr">
         <is>
           <t>Univavá (Classificatória 2)</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="H67" s="6" t="inlineStr">
         <is>
           <t>Cabeça ツ, qweqawq, Triplo, miojo  XTRANHO, p2c</t>
         </is>
       </c>
-      <c r="I67" s="3" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="I67" s="5" t="n"/>
+    </row>
+    <row r="68" ht="15.75" customHeight="1" s="7">
+      <c r="A68" s="6" t="inlineStr">
         <is>
           <t>sistematica_unievangelica</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="6" t="inlineStr">
         <is>
           <t>Sistematica UniEVANGÉLICA</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr"/>
-      <c r="D68" s="3" t="inlineStr"/>
-      <c r="E68" s="3" t="inlineStr"/>
-      <c r="F68" t="n">
+      <c r="C68" s="5" t="n"/>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>Sistema U</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>Universidade Evangélica de Goiás</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G68" s="6" t="inlineStr">
         <is>
           <t>Univavá (Classificatória 4)</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="H68" s="6" t="inlineStr">
         <is>
           <t>JF冷殺手, mattheex, Joji, enzokawai, prido1227</t>
         </is>
       </c>
-      <c r="I68" s="3" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="I68" s="5" t="n"/>
+    </row>
+    <row r="69" ht="15.75" customHeight="1" s="7">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t>nox_unievangelica</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="6" t="inlineStr">
         <is>
           <t>Nox UniEVANGÉLICA</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr"/>
-      <c r="D69" s="3" t="inlineStr"/>
-      <c r="E69" s="3" t="inlineStr"/>
-      <c r="F69" t="n">
+      <c r="C69" s="5" t="n"/>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>Nox</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>Universidade Evangélica de Goiás</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G69" s="6" t="inlineStr">
         <is>
           <t>Univavá (Classificatória 4)</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="H69" s="6" t="inlineStr">
         <is>
           <t>Yuuketts, sonoflickzx, PLUKAS, Nyolzheimer, eddyflickzx</t>
         </is>
       </c>
-      <c r="I69" s="3" t="inlineStr"/>
-    </row>
+      <c r="I69" s="5" t="n"/>
+    </row>
+    <row r="70" ht="15.75" customHeight="1" s="7"/>
+    <row r="71" ht="15.75" customHeight="1" s="7"/>
+    <row r="72" ht="15.75" customHeight="1" s="7"/>
+    <row r="73" ht="15.75" customHeight="1" s="7"/>
+    <row r="74" ht="15.75" customHeight="1" s="7"/>
+    <row r="75" ht="15.75" customHeight="1" s="7"/>
+    <row r="76" ht="15.75" customHeight="1" s="7"/>
+    <row r="77" ht="15.75" customHeight="1" s="7"/>
+    <row r="78" ht="15.75" customHeight="1" s="7"/>
+    <row r="79" ht="15.75" customHeight="1" s="7"/>
+    <row r="80" ht="15.75" customHeight="1" s="7"/>
+    <row r="81" ht="15.75" customHeight="1" s="7"/>
+    <row r="82" ht="15.75" customHeight="1" s="7"/>
+    <row r="83" ht="15.75" customHeight="1" s="7"/>
+    <row r="84" ht="15.75" customHeight="1" s="7"/>
+    <row r="85" ht="15.75" customHeight="1" s="7"/>
+    <row r="86" ht="15.75" customHeight="1" s="7"/>
+    <row r="87" ht="15.75" customHeight="1" s="7"/>
+    <row r="88" ht="15.75" customHeight="1" s="7"/>
+    <row r="89" ht="15.75" customHeight="1" s="7"/>
+    <row r="90" ht="15.75" customHeight="1" s="7"/>
+    <row r="91" ht="15.75" customHeight="1" s="7"/>
+    <row r="92" ht="15.75" customHeight="1" s="7"/>
+    <row r="93" ht="15.75" customHeight="1" s="7"/>
+    <row r="94" ht="15.75" customHeight="1" s="7"/>
+    <row r="95" ht="15.75" customHeight="1" s="7"/>
+    <row r="96" ht="15.75" customHeight="1" s="7"/>
+    <row r="97" ht="15.75" customHeight="1" s="7"/>
+    <row r="98" ht="15.75" customHeight="1" s="7"/>
+    <row r="99" ht="15.75" customHeight="1" s="7"/>
+    <row r="100" ht="15.75" customHeight="1" s="7"/>
+    <row r="101" ht="15.75" customHeight="1" s="7"/>
+    <row r="102" ht="15.75" customHeight="1" s="7"/>
+    <row r="103" ht="15.75" customHeight="1" s="7"/>
+    <row r="104" ht="15.75" customHeight="1" s="7"/>
+    <row r="105" ht="15.75" customHeight="1" s="7"/>
+    <row r="106" ht="15.75" customHeight="1" s="7"/>
+    <row r="107" ht="15.75" customHeight="1" s="7"/>
+    <row r="108" ht="15.75" customHeight="1" s="7"/>
+    <row r="109" ht="15.75" customHeight="1" s="7"/>
+    <row r="110" ht="15.75" customHeight="1" s="7"/>
+    <row r="111" ht="15.75" customHeight="1" s="7"/>
+    <row r="112" ht="15.75" customHeight="1" s="7"/>
+    <row r="113" ht="15.75" customHeight="1" s="7"/>
+    <row r="114" ht="15.75" customHeight="1" s="7"/>
+    <row r="115" ht="15.75" customHeight="1" s="7"/>
+    <row r="116" ht="15.75" customHeight="1" s="7"/>
+    <row r="117" ht="15.75" customHeight="1" s="7"/>
+    <row r="118" ht="15.75" customHeight="1" s="7"/>
+    <row r="119" ht="15.75" customHeight="1" s="7"/>
+    <row r="120" ht="15.75" customHeight="1" s="7"/>
+    <row r="121" ht="15.75" customHeight="1" s="7"/>
+    <row r="122" ht="15.75" customHeight="1" s="7"/>
+    <row r="123" ht="15.75" customHeight="1" s="7"/>
+    <row r="124" ht="15.75" customHeight="1" s="7"/>
+    <row r="125" ht="15.75" customHeight="1" s="7"/>
+    <row r="126" ht="15.75" customHeight="1" s="7"/>
+    <row r="127" ht="15.75" customHeight="1" s="7"/>
+    <row r="128" ht="15.75" customHeight="1" s="7"/>
+    <row r="129" ht="15.75" customHeight="1" s="7"/>
+    <row r="130" ht="15.75" customHeight="1" s="7"/>
+    <row r="131" ht="15.75" customHeight="1" s="7"/>
+    <row r="132" ht="15.75" customHeight="1" s="7"/>
+    <row r="133" ht="15.75" customHeight="1" s="7"/>
+    <row r="134" ht="15.75" customHeight="1" s="7"/>
+    <row r="135" ht="15.75" customHeight="1" s="7"/>
+    <row r="136" ht="15.75" customHeight="1" s="7"/>
+    <row r="137" ht="15.75" customHeight="1" s="7"/>
+    <row r="138" ht="15.75" customHeight="1" s="7"/>
+    <row r="139" ht="15.75" customHeight="1" s="7"/>
+    <row r="140" ht="15.75" customHeight="1" s="7"/>
+    <row r="141" ht="15.75" customHeight="1" s="7"/>
+    <row r="142" ht="15.75" customHeight="1" s="7"/>
+    <row r="143" ht="15.75" customHeight="1" s="7"/>
+    <row r="144" ht="15.75" customHeight="1" s="7"/>
+    <row r="145" ht="15.75" customHeight="1" s="7"/>
+    <row r="146" ht="15.75" customHeight="1" s="7"/>
+    <row r="147" ht="15.75" customHeight="1" s="7"/>
+    <row r="148" ht="15.75" customHeight="1" s="7"/>
+    <row r="149" ht="15.75" customHeight="1" s="7"/>
+    <row r="150" ht="15.75" customHeight="1" s="7"/>
+    <row r="151" ht="15.75" customHeight="1" s="7"/>
+    <row r="152" ht="15.75" customHeight="1" s="7"/>
+    <row r="153" ht="15.75" customHeight="1" s="7"/>
+    <row r="154" ht="15.75" customHeight="1" s="7"/>
+    <row r="155" ht="15.75" customHeight="1" s="7"/>
+    <row r="156" ht="15.75" customHeight="1" s="7"/>
+    <row r="157" ht="15.75" customHeight="1" s="7"/>
+    <row r="158" ht="15.75" customHeight="1" s="7"/>
+    <row r="159" ht="15.75" customHeight="1" s="7"/>
+    <row r="160" ht="15.75" customHeight="1" s="7"/>
+    <row r="161" ht="15.75" customHeight="1" s="7"/>
+    <row r="162" ht="15.75" customHeight="1" s="7"/>
+    <row r="163" ht="15.75" customHeight="1" s="7"/>
+    <row r="164" ht="15.75" customHeight="1" s="7"/>
+    <row r="165" ht="15.75" customHeight="1" s="7"/>
+    <row r="166" ht="15.75" customHeight="1" s="7"/>
+    <row r="167" ht="15.75" customHeight="1" s="7"/>
+    <row r="168" ht="15.75" customHeight="1" s="7"/>
+    <row r="169" ht="15.75" customHeight="1" s="7"/>
+    <row r="170" ht="15.75" customHeight="1" s="7"/>
+    <row r="171" ht="15.75" customHeight="1" s="7"/>
+    <row r="172" ht="15.75" customHeight="1" s="7"/>
+    <row r="173" ht="15.75" customHeight="1" s="7"/>
+    <row r="174" ht="15.75" customHeight="1" s="7"/>
+    <row r="175" ht="15.75" customHeight="1" s="7"/>
+    <row r="176" ht="15.75" customHeight="1" s="7"/>
+    <row r="177" ht="15.75" customHeight="1" s="7"/>
+    <row r="178" ht="15.75" customHeight="1" s="7"/>
+    <row r="179" ht="15.75" customHeight="1" s="7"/>
+    <row r="180" ht="15.75" customHeight="1" s="7"/>
+    <row r="181" ht="15.75" customHeight="1" s="7"/>
+    <row r="182" ht="15.75" customHeight="1" s="7"/>
+    <row r="183" ht="15.75" customHeight="1" s="7"/>
+    <row r="184" ht="15.75" customHeight="1" s="7"/>
+    <row r="185" ht="15.75" customHeight="1" s="7"/>
+    <row r="186" ht="15.75" customHeight="1" s="7"/>
+    <row r="187" ht="15.75" customHeight="1" s="7"/>
+    <row r="188" ht="15.75" customHeight="1" s="7"/>
+    <row r="189" ht="15.75" customHeight="1" s="7"/>
+    <row r="190" ht="15.75" customHeight="1" s="7"/>
+    <row r="191" ht="15.75" customHeight="1" s="7"/>
+    <row r="192" ht="15.75" customHeight="1" s="7"/>
+    <row r="193" ht="15.75" customHeight="1" s="7"/>
+    <row r="194" ht="15.75" customHeight="1" s="7"/>
+    <row r="195" ht="15.75" customHeight="1" s="7"/>
+    <row r="196" ht="15.75" customHeight="1" s="7"/>
+    <row r="197" ht="15.75" customHeight="1" s="7"/>
+    <row r="198" ht="15.75" customHeight="1" s="7"/>
+    <row r="199" ht="15.75" customHeight="1" s="7"/>
+    <row r="200" ht="15.75" customHeight="1" s="7"/>
+    <row r="201" ht="15.75" customHeight="1" s="7"/>
+    <row r="202" ht="15.75" customHeight="1" s="7"/>
+    <row r="203" ht="15.75" customHeight="1" s="7"/>
+    <row r="204" ht="15.75" customHeight="1" s="7"/>
+    <row r="205" ht="15.75" customHeight="1" s="7"/>
+    <row r="206" ht="15.75" customHeight="1" s="7"/>
+    <row r="207" ht="15.75" customHeight="1" s="7"/>
+    <row r="208" ht="15.75" customHeight="1" s="7"/>
+    <row r="209" ht="15.75" customHeight="1" s="7"/>
+    <row r="210" ht="15.75" customHeight="1" s="7"/>
+    <row r="211" ht="15.75" customHeight="1" s="7"/>
+    <row r="212" ht="15.75" customHeight="1" s="7"/>
+    <row r="213" ht="15.75" customHeight="1" s="7"/>
+    <row r="214" ht="15.75" customHeight="1" s="7"/>
+    <row r="215" ht="15.75" customHeight="1" s="7"/>
+    <row r="216" ht="15.75" customHeight="1" s="7"/>
+    <row r="217" ht="15.75" customHeight="1" s="7"/>
+    <row r="218" ht="15.75" customHeight="1" s="7"/>
+    <row r="219" ht="15.75" customHeight="1" s="7"/>
+    <row r="220" ht="15.75" customHeight="1" s="7"/>
+    <row r="221" ht="15.75" customHeight="1" s="7"/>
+    <row r="222" ht="15.75" customHeight="1" s="7"/>
+    <row r="223" ht="15.75" customHeight="1" s="7"/>
+    <row r="224" ht="15.75" customHeight="1" s="7"/>
+    <row r="225" ht="15.75" customHeight="1" s="7"/>
+    <row r="226" ht="15.75" customHeight="1" s="7"/>
+    <row r="227" ht="15.75" customHeight="1" s="7"/>
+    <row r="228" ht="15.75" customHeight="1" s="7"/>
+    <row r="229" ht="15.75" customHeight="1" s="7"/>
+    <row r="230" ht="15.75" customHeight="1" s="7"/>
+    <row r="231" ht="15.75" customHeight="1" s="7"/>
+    <row r="232" ht="15.75" customHeight="1" s="7"/>
+    <row r="233" ht="15.75" customHeight="1" s="7"/>
+    <row r="234" ht="15.75" customHeight="1" s="7"/>
+    <row r="235" ht="15.75" customHeight="1" s="7"/>
+    <row r="236" ht="15.75" customHeight="1" s="7"/>
+    <row r="237" ht="15.75" customHeight="1" s="7"/>
+    <row r="238" ht="15.75" customHeight="1" s="7"/>
+    <row r="239" ht="15.75" customHeight="1" s="7"/>
+    <row r="240" ht="15.75" customHeight="1" s="7"/>
+    <row r="241" ht="15.75" customHeight="1" s="7"/>
+    <row r="242" ht="15.75" customHeight="1" s="7"/>
+    <row r="243" ht="15.75" customHeight="1" s="7"/>
+    <row r="244" ht="15.75" customHeight="1" s="7"/>
+    <row r="245" ht="15.75" customHeight="1" s="7"/>
+    <row r="246" ht="15.75" customHeight="1" s="7"/>
+    <row r="247" ht="15.75" customHeight="1" s="7"/>
+    <row r="248" ht="15.75" customHeight="1" s="7"/>
+    <row r="249" ht="15.75" customHeight="1" s="7"/>
+    <row r="250" ht="15.75" customHeight="1" s="7"/>
+    <row r="251" ht="15.75" customHeight="1" s="7"/>
+    <row r="252" ht="15.75" customHeight="1" s="7"/>
+    <row r="253" ht="15.75" customHeight="1" s="7"/>
+    <row r="254" ht="15.75" customHeight="1" s="7"/>
+    <row r="255" ht="15.75" customHeight="1" s="7"/>
+    <row r="256" ht="15.75" customHeight="1" s="7"/>
+    <row r="257" ht="15.75" customHeight="1" s="7"/>
+    <row r="258" ht="15.75" customHeight="1" s="7"/>
+    <row r="259" ht="15.75" customHeight="1" s="7"/>
+    <row r="260" ht="15.75" customHeight="1" s="7"/>
+    <row r="261" ht="15.75" customHeight="1" s="7"/>
+    <row r="262" ht="15.75" customHeight="1" s="7"/>
+    <row r="263" ht="15.75" customHeight="1" s="7"/>
+    <row r="264" ht="15.75" customHeight="1" s="7"/>
+    <row r="265" ht="15.75" customHeight="1" s="7"/>
+    <row r="266" ht="15.75" customHeight="1" s="7"/>
+    <row r="267" ht="15.75" customHeight="1" s="7"/>
+    <row r="268" ht="15.75" customHeight="1" s="7"/>
+    <row r="269" ht="15.75" customHeight="1" s="7"/>
+    <row r="270" ht="15.75" customHeight="1" s="7"/>
+    <row r="271" ht="15.75" customHeight="1" s="7"/>
+    <row r="272" ht="15.75" customHeight="1" s="7"/>
+    <row r="273" ht="15.75" customHeight="1" s="7"/>
+    <row r="274" ht="15.75" customHeight="1" s="7"/>
+    <row r="275" ht="15.75" customHeight="1" s="7"/>
+    <row r="276" ht="15.75" customHeight="1" s="7"/>
+    <row r="277" ht="15.75" customHeight="1" s="7"/>
+    <row r="278" ht="15.75" customHeight="1" s="7"/>
+    <row r="279" ht="15.75" customHeight="1" s="7"/>
+    <row r="280" ht="15.75" customHeight="1" s="7"/>
+    <row r="281" ht="15.75" customHeight="1" s="7"/>
+    <row r="282" ht="15.75" customHeight="1" s="7"/>
+    <row r="283" ht="15.75" customHeight="1" s="7"/>
+    <row r="284" ht="15.75" customHeight="1" s="7"/>
+    <row r="285" ht="15.75" customHeight="1" s="7"/>
+    <row r="286" ht="15.75" customHeight="1" s="7"/>
+    <row r="287" ht="15.75" customHeight="1" s="7"/>
+    <row r="288" ht="15.75" customHeight="1" s="7"/>
+    <row r="289" ht="15.75" customHeight="1" s="7"/>
+    <row r="290" ht="15.75" customHeight="1" s="7"/>
+    <row r="291" ht="15.75" customHeight="1" s="7"/>
+    <row r="292" ht="15.75" customHeight="1" s="7"/>
+    <row r="293" ht="15.75" customHeight="1" s="7"/>
+    <row r="294" ht="15.75" customHeight="1" s="7"/>
+    <row r="295" ht="15.75" customHeight="1" s="7"/>
+    <row r="296" ht="15.75" customHeight="1" s="7"/>
+    <row r="297" ht="15.75" customHeight="1" s="7"/>
+    <row r="298" ht="15.75" customHeight="1" s="7"/>
+    <row r="299" ht="15.75" customHeight="1" s="7"/>
+    <row r="300" ht="15.75" customHeight="1" s="7"/>
+    <row r="301" ht="15.75" customHeight="1" s="7"/>
+    <row r="302" ht="15.75" customHeight="1" s="7"/>
+    <row r="303" ht="15.75" customHeight="1" s="7"/>
+    <row r="304" ht="15.75" customHeight="1" s="7"/>
+    <row r="305" ht="15.75" customHeight="1" s="7"/>
+    <row r="306" ht="15.75" customHeight="1" s="7"/>
+    <row r="307" ht="15.75" customHeight="1" s="7"/>
+    <row r="308" ht="15.75" customHeight="1" s="7"/>
+    <row r="309" ht="15.75" customHeight="1" s="7"/>
+    <row r="310" ht="15.75" customHeight="1" s="7"/>
+    <row r="311" ht="15.75" customHeight="1" s="7"/>
+    <row r="312" ht="15.75" customHeight="1" s="7"/>
+    <row r="313" ht="15.75" customHeight="1" s="7"/>
+    <row r="314" ht="15.75" customHeight="1" s="7"/>
+    <row r="315" ht="15.75" customHeight="1" s="7"/>
+    <row r="316" ht="15.75" customHeight="1" s="7"/>
+    <row r="317" ht="15.75" customHeight="1" s="7"/>
+    <row r="318" ht="15.75" customHeight="1" s="7"/>
+    <row r="319" ht="15.75" customHeight="1" s="7"/>
+    <row r="320" ht="15.75" customHeight="1" s="7"/>
+    <row r="321" ht="15.75" customHeight="1" s="7"/>
+    <row r="322" ht="15.75" customHeight="1" s="7"/>
+    <row r="323" ht="15.75" customHeight="1" s="7"/>
+    <row r="324" ht="15.75" customHeight="1" s="7"/>
+    <row r="325" ht="15.75" customHeight="1" s="7"/>
+    <row r="326" ht="15.75" customHeight="1" s="7"/>
+    <row r="327" ht="15.75" customHeight="1" s="7"/>
+    <row r="328" ht="15.75" customHeight="1" s="7"/>
+    <row r="329" ht="15.75" customHeight="1" s="7"/>
+    <row r="330" ht="15.75" customHeight="1" s="7"/>
+    <row r="331" ht="15.75" customHeight="1" s="7"/>
+    <row r="332" ht="15.75" customHeight="1" s="7"/>
+    <row r="333" ht="15.75" customHeight="1" s="7"/>
+    <row r="334" ht="15.75" customHeight="1" s="7"/>
+    <row r="335" ht="15.75" customHeight="1" s="7"/>
+    <row r="336" ht="15.75" customHeight="1" s="7"/>
+    <row r="337" ht="15.75" customHeight="1" s="7"/>
+    <row r="338" ht="15.75" customHeight="1" s="7"/>
+    <row r="339" ht="15.75" customHeight="1" s="7"/>
+    <row r="340" ht="15.75" customHeight="1" s="7"/>
+    <row r="341" ht="15.75" customHeight="1" s="7"/>
+    <row r="342" ht="15.75" customHeight="1" s="7"/>
+    <row r="343" ht="15.75" customHeight="1" s="7"/>
+    <row r="344" ht="15.75" customHeight="1" s="7"/>
+    <row r="345" ht="15.75" customHeight="1" s="7"/>
+    <row r="346" ht="15.75" customHeight="1" s="7"/>
+    <row r="347" ht="15.75" customHeight="1" s="7"/>
+    <row r="348" ht="15.75" customHeight="1" s="7"/>
+    <row r="349" ht="15.75" customHeight="1" s="7"/>
+    <row r="350" ht="15.75" customHeight="1" s="7"/>
+    <row r="351" ht="15.75" customHeight="1" s="7"/>
+    <row r="352" ht="15.75" customHeight="1" s="7"/>
+    <row r="353" ht="15.75" customHeight="1" s="7"/>
+    <row r="354" ht="15.75" customHeight="1" s="7"/>
+    <row r="355" ht="15.75" customHeight="1" s="7"/>
+    <row r="356" ht="15.75" customHeight="1" s="7"/>
+    <row r="357" ht="15.75" customHeight="1" s="7"/>
+    <row r="358" ht="15.75" customHeight="1" s="7"/>
+    <row r="359" ht="15.75" customHeight="1" s="7"/>
+    <row r="360" ht="15.75" customHeight="1" s="7"/>
+    <row r="361" ht="15.75" customHeight="1" s="7"/>
+    <row r="362" ht="15.75" customHeight="1" s="7"/>
+    <row r="363" ht="15.75" customHeight="1" s="7"/>
+    <row r="364" ht="15.75" customHeight="1" s="7"/>
+    <row r="365" ht="15.75" customHeight="1" s="7"/>
+    <row r="366" ht="15.75" customHeight="1" s="7"/>
+    <row r="367" ht="15.75" customHeight="1" s="7"/>
+    <row r="368" ht="15.75" customHeight="1" s="7"/>
+    <row r="369" ht="15.75" customHeight="1" s="7"/>
+    <row r="370" ht="15.75" customHeight="1" s="7"/>
+    <row r="371" ht="15.75" customHeight="1" s="7"/>
+    <row r="372" ht="15.75" customHeight="1" s="7"/>
+    <row r="373" ht="15.75" customHeight="1" s="7"/>
+    <row r="374" ht="15.75" customHeight="1" s="7"/>
+    <row r="375" ht="15.75" customHeight="1" s="7"/>
+    <row r="376" ht="15.75" customHeight="1" s="7"/>
+    <row r="377" ht="15.75" customHeight="1" s="7"/>
+    <row r="378" ht="15.75" customHeight="1" s="7"/>
+    <row r="379" ht="15.75" customHeight="1" s="7"/>
+    <row r="380" ht="15.75" customHeight="1" s="7"/>
+    <row r="381" ht="15.75" customHeight="1" s="7"/>
+    <row r="382" ht="15.75" customHeight="1" s="7"/>
+    <row r="383" ht="15.75" customHeight="1" s="7"/>
+    <row r="384" ht="15.75" customHeight="1" s="7"/>
+    <row r="385" ht="15.75" customHeight="1" s="7"/>
+    <row r="386" ht="15.75" customHeight="1" s="7"/>
+    <row r="387" ht="15.75" customHeight="1" s="7"/>
+    <row r="388" ht="15.75" customHeight="1" s="7"/>
+    <row r="389" ht="15.75" customHeight="1" s="7"/>
+    <row r="390" ht="15.75" customHeight="1" s="7"/>
+    <row r="391" ht="15.75" customHeight="1" s="7"/>
+    <row r="392" ht="15.75" customHeight="1" s="7"/>
+    <row r="393" ht="15.75" customHeight="1" s="7"/>
+    <row r="394" ht="15.75" customHeight="1" s="7"/>
+    <row r="395" ht="15.75" customHeight="1" s="7"/>
+    <row r="396" ht="15.75" customHeight="1" s="7"/>
+    <row r="397" ht="15.75" customHeight="1" s="7"/>
+    <row r="398" ht="15.75" customHeight="1" s="7"/>
+    <row r="399" ht="15.75" customHeight="1" s="7"/>
+    <row r="400" ht="15.75" customHeight="1" s="7"/>
+    <row r="401" ht="15.75" customHeight="1" s="7"/>
+    <row r="402" ht="15.75" customHeight="1" s="7"/>
+    <row r="403" ht="15.75" customHeight="1" s="7"/>
+    <row r="404" ht="15.75" customHeight="1" s="7"/>
+    <row r="405" ht="15.75" customHeight="1" s="7"/>
+    <row r="406" ht="15.75" customHeight="1" s="7"/>
+    <row r="407" ht="15.75" customHeight="1" s="7"/>
+    <row r="408" ht="15.75" customHeight="1" s="7"/>
+    <row r="409" ht="15.75" customHeight="1" s="7"/>
+    <row r="410" ht="15.75" customHeight="1" s="7"/>
+    <row r="411" ht="15.75" customHeight="1" s="7"/>
+    <row r="412" ht="15.75" customHeight="1" s="7"/>
+    <row r="413" ht="15.75" customHeight="1" s="7"/>
+    <row r="414" ht="15.75" customHeight="1" s="7"/>
+    <row r="415" ht="15.75" customHeight="1" s="7"/>
+    <row r="416" ht="15.75" customHeight="1" s="7"/>
+    <row r="417" ht="15.75" customHeight="1" s="7"/>
+    <row r="418" ht="15.75" customHeight="1" s="7"/>
+    <row r="419" ht="15.75" customHeight="1" s="7"/>
+    <row r="420" ht="15.75" customHeight="1" s="7"/>
+    <row r="421" ht="15.75" customHeight="1" s="7"/>
+    <row r="422" ht="15.75" customHeight="1" s="7"/>
+    <row r="423" ht="15.75" customHeight="1" s="7"/>
+    <row r="424" ht="15.75" customHeight="1" s="7"/>
+    <row r="425" ht="15.75" customHeight="1" s="7"/>
+    <row r="426" ht="15.75" customHeight="1" s="7"/>
+    <row r="427" ht="15.75" customHeight="1" s="7"/>
+    <row r="428" ht="15.75" customHeight="1" s="7"/>
+    <row r="429" ht="15.75" customHeight="1" s="7"/>
+    <row r="430" ht="15.75" customHeight="1" s="7"/>
+    <row r="431" ht="15.75" customHeight="1" s="7"/>
+    <row r="432" ht="15.75" customHeight="1" s="7"/>
+    <row r="433" ht="15.75" customHeight="1" s="7"/>
+    <row r="434" ht="15.75" customHeight="1" s="7"/>
+    <row r="435" ht="15.75" customHeight="1" s="7"/>
+    <row r="436" ht="15.75" customHeight="1" s="7"/>
+    <row r="437" ht="15.75" customHeight="1" s="7"/>
+    <row r="438" ht="15.75" customHeight="1" s="7"/>
+    <row r="439" ht="15.75" customHeight="1" s="7"/>
+    <row r="440" ht="15.75" customHeight="1" s="7"/>
+    <row r="441" ht="15.75" customHeight="1" s="7"/>
+    <row r="442" ht="15.75" customHeight="1" s="7"/>
+    <row r="443" ht="15.75" customHeight="1" s="7"/>
+    <row r="444" ht="15.75" customHeight="1" s="7"/>
+    <row r="445" ht="15.75" customHeight="1" s="7"/>
+    <row r="446" ht="15.75" customHeight="1" s="7"/>
+    <row r="447" ht="15.75" customHeight="1" s="7"/>
+    <row r="448" ht="15.75" customHeight="1" s="7"/>
+    <row r="449" ht="15.75" customHeight="1" s="7"/>
+    <row r="450" ht="15.75" customHeight="1" s="7"/>
+    <row r="451" ht="15.75" customHeight="1" s="7"/>
+    <row r="452" ht="15.75" customHeight="1" s="7"/>
+    <row r="453" ht="15.75" customHeight="1" s="7"/>
+    <row r="454" ht="15.75" customHeight="1" s="7"/>
+    <row r="455" ht="15.75" customHeight="1" s="7"/>
+    <row r="456" ht="15.75" customHeight="1" s="7"/>
+    <row r="457" ht="15.75" customHeight="1" s="7"/>
+    <row r="458" ht="15.75" customHeight="1" s="7"/>
+    <row r="459" ht="15.75" customHeight="1" s="7"/>
+    <row r="460" ht="15.75" customHeight="1" s="7"/>
+    <row r="461" ht="15.75" customHeight="1" s="7"/>
+    <row r="462" ht="15.75" customHeight="1" s="7"/>
+    <row r="463" ht="15.75" customHeight="1" s="7"/>
+    <row r="464" ht="15.75" customHeight="1" s="7"/>
+    <row r="465" ht="15.75" customHeight="1" s="7"/>
+    <row r="466" ht="15.75" customHeight="1" s="7"/>
+    <row r="467" ht="15.75" customHeight="1" s="7"/>
+    <row r="468" ht="15.75" customHeight="1" s="7"/>
+    <row r="469" ht="15.75" customHeight="1" s="7"/>
+    <row r="470" ht="15.75" customHeight="1" s="7"/>
+    <row r="471" ht="15.75" customHeight="1" s="7"/>
+    <row r="472" ht="15.75" customHeight="1" s="7"/>
+    <row r="473" ht="15.75" customHeight="1" s="7"/>
+    <row r="474" ht="15.75" customHeight="1" s="7"/>
+    <row r="475" ht="15.75" customHeight="1" s="7"/>
+    <row r="476" ht="15.75" customHeight="1" s="7"/>
+    <row r="477" ht="15.75" customHeight="1" s="7"/>
+    <row r="478" ht="15.75" customHeight="1" s="7"/>
+    <row r="479" ht="15.75" customHeight="1" s="7"/>
+    <row r="480" ht="15.75" customHeight="1" s="7"/>
+    <row r="481" ht="15.75" customHeight="1" s="7"/>
+    <row r="482" ht="15.75" customHeight="1" s="7"/>
+    <row r="483" ht="15.75" customHeight="1" s="7"/>
+    <row r="484" ht="15.75" customHeight="1" s="7"/>
+    <row r="485" ht="15.75" customHeight="1" s="7"/>
+    <row r="486" ht="15.75" customHeight="1" s="7"/>
+    <row r="487" ht="15.75" customHeight="1" s="7"/>
+    <row r="488" ht="15.75" customHeight="1" s="7"/>
+    <row r="489" ht="15.75" customHeight="1" s="7"/>
+    <row r="490" ht="15.75" customHeight="1" s="7"/>
+    <row r="491" ht="15.75" customHeight="1" s="7"/>
+    <row r="492" ht="15.75" customHeight="1" s="7"/>
+    <row r="493" ht="15.75" customHeight="1" s="7"/>
+    <row r="494" ht="15.75" customHeight="1" s="7"/>
+    <row r="495" ht="15.75" customHeight="1" s="7"/>
+    <row r="496" ht="15.75" customHeight="1" s="7"/>
+    <row r="497" ht="15.75" customHeight="1" s="7"/>
+    <row r="498" ht="15.75" customHeight="1" s="7"/>
+    <row r="499" ht="15.75" customHeight="1" s="7"/>
+    <row r="500" ht="15.75" customHeight="1" s="7"/>
+    <row r="501" ht="15.75" customHeight="1" s="7"/>
+    <row r="502" ht="15.75" customHeight="1" s="7"/>
+    <row r="503" ht="15.75" customHeight="1" s="7"/>
+    <row r="504" ht="15.75" customHeight="1" s="7"/>
+    <row r="505" ht="15.75" customHeight="1" s="7"/>
+    <row r="506" ht="15.75" customHeight="1" s="7"/>
+    <row r="507" ht="15.75" customHeight="1" s="7"/>
+    <row r="508" ht="15.75" customHeight="1" s="7"/>
+    <row r="509" ht="15.75" customHeight="1" s="7"/>
+    <row r="510" ht="15.75" customHeight="1" s="7"/>
+    <row r="511" ht="15.75" customHeight="1" s="7"/>
+    <row r="512" ht="15.75" customHeight="1" s="7"/>
+    <row r="513" ht="15.75" customHeight="1" s="7"/>
+    <row r="514" ht="15.75" customHeight="1" s="7"/>
+    <row r="515" ht="15.75" customHeight="1" s="7"/>
+    <row r="516" ht="15.75" customHeight="1" s="7"/>
+    <row r="517" ht="15.75" customHeight="1" s="7"/>
+    <row r="518" ht="15.75" customHeight="1" s="7"/>
+    <row r="519" ht="15.75" customHeight="1" s="7"/>
+    <row r="520" ht="15.75" customHeight="1" s="7"/>
+    <row r="521" ht="15.75" customHeight="1" s="7"/>
+    <row r="522" ht="15.75" customHeight="1" s="7"/>
+    <row r="523" ht="15.75" customHeight="1" s="7"/>
+    <row r="524" ht="15.75" customHeight="1" s="7"/>
+    <row r="525" ht="15.75" customHeight="1" s="7"/>
+    <row r="526" ht="15.75" customHeight="1" s="7"/>
+    <row r="527" ht="15.75" customHeight="1" s="7"/>
+    <row r="528" ht="15.75" customHeight="1" s="7"/>
+    <row r="529" ht="15.75" customHeight="1" s="7"/>
+    <row r="530" ht="15.75" customHeight="1" s="7"/>
+    <row r="531" ht="15.75" customHeight="1" s="7"/>
+    <row r="532" ht="15.75" customHeight="1" s="7"/>
+    <row r="533" ht="15.75" customHeight="1" s="7"/>
+    <row r="534" ht="15.75" customHeight="1" s="7"/>
+    <row r="535" ht="15.75" customHeight="1" s="7"/>
+    <row r="536" ht="15.75" customHeight="1" s="7"/>
+    <row r="537" ht="15.75" customHeight="1" s="7"/>
+    <row r="538" ht="15.75" customHeight="1" s="7"/>
+    <row r="539" ht="15.75" customHeight="1" s="7"/>
+    <row r="540" ht="15.75" customHeight="1" s="7"/>
+    <row r="541" ht="15.75" customHeight="1" s="7"/>
+    <row r="542" ht="15.75" customHeight="1" s="7"/>
+    <row r="543" ht="15.75" customHeight="1" s="7"/>
+    <row r="544" ht="15.75" customHeight="1" s="7"/>
+    <row r="545" ht="15.75" customHeight="1" s="7"/>
+    <row r="546" ht="15.75" customHeight="1" s="7"/>
+    <row r="547" ht="15.75" customHeight="1" s="7"/>
+    <row r="548" ht="15.75" customHeight="1" s="7"/>
+    <row r="549" ht="15.75" customHeight="1" s="7"/>
+    <row r="550" ht="15.75" customHeight="1" s="7"/>
+    <row r="551" ht="15.75" customHeight="1" s="7"/>
+    <row r="552" ht="15.75" customHeight="1" s="7"/>
+    <row r="553" ht="15.75" customHeight="1" s="7"/>
+    <row r="554" ht="15.75" customHeight="1" s="7"/>
+    <row r="555" ht="15.75" customHeight="1" s="7"/>
+    <row r="556" ht="15.75" customHeight="1" s="7"/>
+    <row r="557" ht="15.75" customHeight="1" s="7"/>
+    <row r="558" ht="15.75" customHeight="1" s="7"/>
+    <row r="559" ht="15.75" customHeight="1" s="7"/>
+    <row r="560" ht="15.75" customHeight="1" s="7"/>
+    <row r="561" ht="15.75" customHeight="1" s="7"/>
+    <row r="562" ht="15.75" customHeight="1" s="7"/>
+    <row r="563" ht="15.75" customHeight="1" s="7"/>
+    <row r="564" ht="15.75" customHeight="1" s="7"/>
+    <row r="565" ht="15.75" customHeight="1" s="7"/>
+    <row r="566" ht="15.75" customHeight="1" s="7"/>
+    <row r="567" ht="15.75" customHeight="1" s="7"/>
+    <row r="568" ht="15.75" customHeight="1" s="7"/>
+    <row r="569" ht="15.75" customHeight="1" s="7"/>
+    <row r="570" ht="15.75" customHeight="1" s="7"/>
+    <row r="571" ht="15.75" customHeight="1" s="7"/>
+    <row r="572" ht="15.75" customHeight="1" s="7"/>
+    <row r="573" ht="15.75" customHeight="1" s="7"/>
+    <row r="574" ht="15.75" customHeight="1" s="7"/>
+    <row r="575" ht="15.75" customHeight="1" s="7"/>
+    <row r="576" ht="15.75" customHeight="1" s="7"/>
+    <row r="577" ht="15.75" customHeight="1" s="7"/>
+    <row r="578" ht="15.75" customHeight="1" s="7"/>
+    <row r="579" ht="15.75" customHeight="1" s="7"/>
+    <row r="580" ht="15.75" customHeight="1" s="7"/>
+    <row r="581" ht="15.75" customHeight="1" s="7"/>
+    <row r="582" ht="15.75" customHeight="1" s="7"/>
+    <row r="583" ht="15.75" customHeight="1" s="7"/>
+    <row r="584" ht="15.75" customHeight="1" s="7"/>
+    <row r="585" ht="15.75" customHeight="1" s="7"/>
+    <row r="586" ht="15.75" customHeight="1" s="7"/>
+    <row r="587" ht="15.75" customHeight="1" s="7"/>
+    <row r="588" ht="15.75" customHeight="1" s="7"/>
+    <row r="589" ht="15.75" customHeight="1" s="7"/>
+    <row r="590" ht="15.75" customHeight="1" s="7"/>
+    <row r="591" ht="15.75" customHeight="1" s="7"/>
+    <row r="592" ht="15.75" customHeight="1" s="7"/>
+    <row r="593" ht="15.75" customHeight="1" s="7"/>
+    <row r="594" ht="15.75" customHeight="1" s="7"/>
+    <row r="595" ht="15.75" customHeight="1" s="7"/>
+    <row r="596" ht="15.75" customHeight="1" s="7"/>
+    <row r="597" ht="15.75" customHeight="1" s="7"/>
+    <row r="598" ht="15.75" customHeight="1" s="7"/>
+    <row r="599" ht="15.75" customHeight="1" s="7"/>
+    <row r="600" ht="15.75" customHeight="1" s="7"/>
+    <row r="601" ht="15.75" customHeight="1" s="7"/>
+    <row r="602" ht="15.75" customHeight="1" s="7"/>
+    <row r="603" ht="15.75" customHeight="1" s="7"/>
+    <row r="604" ht="15.75" customHeight="1" s="7"/>
+    <row r="605" ht="15.75" customHeight="1" s="7"/>
+    <row r="606" ht="15.75" customHeight="1" s="7"/>
+    <row r="607" ht="15.75" customHeight="1" s="7"/>
+    <row r="608" ht="15.75" customHeight="1" s="7"/>
+    <row r="609" ht="15.75" customHeight="1" s="7"/>
+    <row r="610" ht="15.75" customHeight="1" s="7"/>
+    <row r="611" ht="15.75" customHeight="1" s="7"/>
+    <row r="612" ht="15.75" customHeight="1" s="7"/>
+    <row r="613" ht="15.75" customHeight="1" s="7"/>
+    <row r="614" ht="15.75" customHeight="1" s="7"/>
+    <row r="615" ht="15.75" customHeight="1" s="7"/>
+    <row r="616" ht="15.75" customHeight="1" s="7"/>
+    <row r="617" ht="15.75" customHeight="1" s="7"/>
+    <row r="618" ht="15.75" customHeight="1" s="7"/>
+    <row r="619" ht="15.75" customHeight="1" s="7"/>
+    <row r="620" ht="15.75" customHeight="1" s="7"/>
+    <row r="621" ht="15.75" customHeight="1" s="7"/>
+    <row r="622" ht="15.75" customHeight="1" s="7"/>
+    <row r="623" ht="15.75" customHeight="1" s="7"/>
+    <row r="624" ht="15.75" customHeight="1" s="7"/>
+    <row r="625" ht="15.75" customHeight="1" s="7"/>
+    <row r="626" ht="15.75" customHeight="1" s="7"/>
+    <row r="627" ht="15.75" customHeight="1" s="7"/>
+    <row r="628" ht="15.75" customHeight="1" s="7"/>
+    <row r="629" ht="15.75" customHeight="1" s="7"/>
+    <row r="630" ht="15.75" customHeight="1" s="7"/>
+    <row r="631" ht="15.75" customHeight="1" s="7"/>
+    <row r="632" ht="15.75" customHeight="1" s="7"/>
+    <row r="633" ht="15.75" customHeight="1" s="7"/>
+    <row r="634" ht="15.75" customHeight="1" s="7"/>
+    <row r="635" ht="15.75" customHeight="1" s="7"/>
+    <row r="636" ht="15.75" customHeight="1" s="7"/>
+    <row r="637" ht="15.75" customHeight="1" s="7"/>
+    <row r="638" ht="15.75" customHeight="1" s="7"/>
+    <row r="639" ht="15.75" customHeight="1" s="7"/>
+    <row r="640" ht="15.75" customHeight="1" s="7"/>
+    <row r="641" ht="15.75" customHeight="1" s="7"/>
+    <row r="642" ht="15.75" customHeight="1" s="7"/>
+    <row r="643" ht="15.75" customHeight="1" s="7"/>
+    <row r="644" ht="15.75" customHeight="1" s="7"/>
+    <row r="645" ht="15.75" customHeight="1" s="7"/>
+    <row r="646" ht="15.75" customHeight="1" s="7"/>
+    <row r="647" ht="15.75" customHeight="1" s="7"/>
+    <row r="648" ht="15.75" customHeight="1" s="7"/>
+    <row r="649" ht="15.75" customHeight="1" s="7"/>
+    <row r="650" ht="15.75" customHeight="1" s="7"/>
+    <row r="651" ht="15.75" customHeight="1" s="7"/>
+    <row r="652" ht="15.75" customHeight="1" s="7"/>
+    <row r="653" ht="15.75" customHeight="1" s="7"/>
+    <row r="654" ht="15.75" customHeight="1" s="7"/>
+    <row r="655" ht="15.75" customHeight="1" s="7"/>
+    <row r="656" ht="15.75" customHeight="1" s="7"/>
+    <row r="657" ht="15.75" customHeight="1" s="7"/>
+    <row r="658" ht="15.75" customHeight="1" s="7"/>
+    <row r="659" ht="15.75" customHeight="1" s="7"/>
+    <row r="660" ht="15.75" customHeight="1" s="7"/>
+    <row r="661" ht="15.75" customHeight="1" s="7"/>
+    <row r="662" ht="15.75" customHeight="1" s="7"/>
+    <row r="663" ht="15.75" customHeight="1" s="7"/>
+    <row r="664" ht="15.75" customHeight="1" s="7"/>
+    <row r="665" ht="15.75" customHeight="1" s="7"/>
+    <row r="666" ht="15.75" customHeight="1" s="7"/>
+    <row r="667" ht="15.75" customHeight="1" s="7"/>
+    <row r="668" ht="15.75" customHeight="1" s="7"/>
+    <row r="669" ht="15.75" customHeight="1" s="7"/>
+    <row r="670" ht="15.75" customHeight="1" s="7"/>
+    <row r="671" ht="15.75" customHeight="1" s="7"/>
+    <row r="672" ht="15.75" customHeight="1" s="7"/>
+    <row r="673" ht="15.75" customHeight="1" s="7"/>
+    <row r="674" ht="15.75" customHeight="1" s="7"/>
+    <row r="675" ht="15.75" customHeight="1" s="7"/>
+    <row r="676" ht="15.75" customHeight="1" s="7"/>
+    <row r="677" ht="15.75" customHeight="1" s="7"/>
+    <row r="678" ht="15.75" customHeight="1" s="7"/>
+    <row r="679" ht="15.75" customHeight="1" s="7"/>
+    <row r="680" ht="15.75" customHeight="1" s="7"/>
+    <row r="681" ht="15.75" customHeight="1" s="7"/>
+    <row r="682" ht="15.75" customHeight="1" s="7"/>
+    <row r="683" ht="15.75" customHeight="1" s="7"/>
+    <row r="684" ht="15.75" customHeight="1" s="7"/>
+    <row r="685" ht="15.75" customHeight="1" s="7"/>
+    <row r="686" ht="15.75" customHeight="1" s="7"/>
+    <row r="687" ht="15.75" customHeight="1" s="7"/>
+    <row r="688" ht="15.75" customHeight="1" s="7"/>
+    <row r="689" ht="15.75" customHeight="1" s="7"/>
+    <row r="690" ht="15.75" customHeight="1" s="7"/>
+    <row r="691" ht="15.75" customHeight="1" s="7"/>
+    <row r="692" ht="15.75" customHeight="1" s="7"/>
+    <row r="693" ht="15.75" customHeight="1" s="7"/>
+    <row r="694" ht="15.75" customHeight="1" s="7"/>
+    <row r="695" ht="15.75" customHeight="1" s="7"/>
+    <row r="696" ht="15.75" customHeight="1" s="7"/>
+    <row r="697" ht="15.75" customHeight="1" s="7"/>
+    <row r="698" ht="15.75" customHeight="1" s="7"/>
+    <row r="699" ht="15.75" customHeight="1" s="7"/>
+    <row r="700" ht="15.75" customHeight="1" s="7"/>
+    <row r="701" ht="15.75" customHeight="1" s="7"/>
+    <row r="702" ht="15.75" customHeight="1" s="7"/>
+    <row r="703" ht="15.75" customHeight="1" s="7"/>
+    <row r="704" ht="15.75" customHeight="1" s="7"/>
+    <row r="705" ht="15.75" customHeight="1" s="7"/>
+    <row r="706" ht="15.75" customHeight="1" s="7"/>
+    <row r="707" ht="15.75" customHeight="1" s="7"/>
+    <row r="708" ht="15.75" customHeight="1" s="7"/>
+    <row r="709" ht="15.75" customHeight="1" s="7"/>
+    <row r="710" ht="15.75" customHeight="1" s="7"/>
+    <row r="711" ht="15.75" customHeight="1" s="7"/>
+    <row r="712" ht="15.75" customHeight="1" s="7"/>
+    <row r="713" ht="15.75" customHeight="1" s="7"/>
+    <row r="714" ht="15.75" customHeight="1" s="7"/>
+    <row r="715" ht="15.75" customHeight="1" s="7"/>
+    <row r="716" ht="15.75" customHeight="1" s="7"/>
+    <row r="717" ht="15.75" customHeight="1" s="7"/>
+    <row r="718" ht="15.75" customHeight="1" s="7"/>
+    <row r="719" ht="15.75" customHeight="1" s="7"/>
+    <row r="720" ht="15.75" customHeight="1" s="7"/>
+    <row r="721" ht="15.75" customHeight="1" s="7"/>
+    <row r="722" ht="15.75" customHeight="1" s="7"/>
+    <row r="723" ht="15.75" customHeight="1" s="7"/>
+    <row r="724" ht="15.75" customHeight="1" s="7"/>
+    <row r="725" ht="15.75" customHeight="1" s="7"/>
+    <row r="726" ht="15.75" customHeight="1" s="7"/>
+    <row r="727" ht="15.75" customHeight="1" s="7"/>
+    <row r="728" ht="15.75" customHeight="1" s="7"/>
+    <row r="729" ht="15.75" customHeight="1" s="7"/>
+    <row r="730" ht="15.75" customHeight="1" s="7"/>
+    <row r="731" ht="15.75" customHeight="1" s="7"/>
+    <row r="732" ht="15.75" customHeight="1" s="7"/>
+    <row r="733" ht="15.75" customHeight="1" s="7"/>
+    <row r="734" ht="15.75" customHeight="1" s="7"/>
+    <row r="735" ht="15.75" customHeight="1" s="7"/>
+    <row r="736" ht="15.75" customHeight="1" s="7"/>
+    <row r="737" ht="15.75" customHeight="1" s="7"/>
+    <row r="738" ht="15.75" customHeight="1" s="7"/>
+    <row r="739" ht="15.75" customHeight="1" s="7"/>
+    <row r="740" ht="15.75" customHeight="1" s="7"/>
+    <row r="741" ht="15.75" customHeight="1" s="7"/>
+    <row r="742" ht="15.75" customHeight="1" s="7"/>
+    <row r="743" ht="15.75" customHeight="1" s="7"/>
+    <row r="744" ht="15.75" customHeight="1" s="7"/>
+    <row r="745" ht="15.75" customHeight="1" s="7"/>
+    <row r="746" ht="15.75" customHeight="1" s="7"/>
+    <row r="747" ht="15.75" customHeight="1" s="7"/>
+    <row r="748" ht="15.75" customHeight="1" s="7"/>
+    <row r="749" ht="15.75" customHeight="1" s="7"/>
+    <row r="750" ht="15.75" customHeight="1" s="7"/>
+    <row r="751" ht="15.75" customHeight="1" s="7"/>
+    <row r="752" ht="15.75" customHeight="1" s="7"/>
+    <row r="753" ht="15.75" customHeight="1" s="7"/>
+    <row r="754" ht="15.75" customHeight="1" s="7"/>
+    <row r="755" ht="15.75" customHeight="1" s="7"/>
+    <row r="756" ht="15.75" customHeight="1" s="7"/>
+    <row r="757" ht="15.75" customHeight="1" s="7"/>
+    <row r="758" ht="15.75" customHeight="1" s="7"/>
+    <row r="759" ht="15.75" customHeight="1" s="7"/>
+    <row r="760" ht="15.75" customHeight="1" s="7"/>
+    <row r="761" ht="15.75" customHeight="1" s="7"/>
+    <row r="762" ht="15.75" customHeight="1" s="7"/>
+    <row r="763" ht="15.75" customHeight="1" s="7"/>
+    <row r="764" ht="15.75" customHeight="1" s="7"/>
+    <row r="765" ht="15.75" customHeight="1" s="7"/>
+    <row r="766" ht="15.75" customHeight="1" s="7"/>
+    <row r="767" ht="15.75" customHeight="1" s="7"/>
+    <row r="768" ht="15.75" customHeight="1" s="7"/>
+    <row r="769" ht="15.75" customHeight="1" s="7"/>
+    <row r="770" ht="15.75" customHeight="1" s="7"/>
+    <row r="771" ht="15.75" customHeight="1" s="7"/>
+    <row r="772" ht="15.75" customHeight="1" s="7"/>
+    <row r="773" ht="15.75" customHeight="1" s="7"/>
+    <row r="774" ht="15.75" customHeight="1" s="7"/>
+    <row r="775" ht="15.75" customHeight="1" s="7"/>
+    <row r="776" ht="15.75" customHeight="1" s="7"/>
+    <row r="777" ht="15.75" customHeight="1" s="7"/>
+    <row r="778" ht="15.75" customHeight="1" s="7"/>
+    <row r="779" ht="15.75" customHeight="1" s="7"/>
+    <row r="780" ht="15.75" customHeight="1" s="7"/>
+    <row r="781" ht="15.75" customHeight="1" s="7"/>
+    <row r="782" ht="15.75" customHeight="1" s="7"/>
+    <row r="783" ht="15.75" customHeight="1" s="7"/>
+    <row r="784" ht="15.75" customHeight="1" s="7"/>
+    <row r="785" ht="15.75" customHeight="1" s="7"/>
+    <row r="786" ht="15.75" customHeight="1" s="7"/>
+    <row r="787" ht="15.75" customHeight="1" s="7"/>
+    <row r="788" ht="15.75" customHeight="1" s="7"/>
+    <row r="789" ht="15.75" customHeight="1" s="7"/>
+    <row r="790" ht="15.75" customHeight="1" s="7"/>
+    <row r="791" ht="15.75" customHeight="1" s="7"/>
+    <row r="792" ht="15.75" customHeight="1" s="7"/>
+    <row r="793" ht="15.75" customHeight="1" s="7"/>
+    <row r="794" ht="15.75" customHeight="1" s="7"/>
+    <row r="795" ht="15.75" customHeight="1" s="7"/>
+    <row r="796" ht="15.75" customHeight="1" s="7"/>
+    <row r="797" ht="15.75" customHeight="1" s="7"/>
+    <row r="798" ht="15.75" customHeight="1" s="7"/>
+    <row r="799" ht="15.75" customHeight="1" s="7"/>
+    <row r="800" ht="15.75" customHeight="1" s="7"/>
+    <row r="801" ht="15.75" customHeight="1" s="7"/>
+    <row r="802" ht="15.75" customHeight="1" s="7"/>
+    <row r="803" ht="15.75" customHeight="1" s="7"/>
+    <row r="804" ht="15.75" customHeight="1" s="7"/>
+    <row r="805" ht="15.75" customHeight="1" s="7"/>
+    <row r="806" ht="15.75" customHeight="1" s="7"/>
+    <row r="807" ht="15.75" customHeight="1" s="7"/>
+    <row r="808" ht="15.75" customHeight="1" s="7"/>
+    <row r="809" ht="15.75" customHeight="1" s="7"/>
+    <row r="810" ht="15.75" customHeight="1" s="7"/>
+    <row r="811" ht="15.75" customHeight="1" s="7"/>
+    <row r="812" ht="15.75" customHeight="1" s="7"/>
+    <row r="813" ht="15.75" customHeight="1" s="7"/>
+    <row r="814" ht="15.75" customHeight="1" s="7"/>
+    <row r="815" ht="15.75" customHeight="1" s="7"/>
+    <row r="816" ht="15.75" customHeight="1" s="7"/>
+    <row r="817" ht="15.75" customHeight="1" s="7"/>
+    <row r="818" ht="15.75" customHeight="1" s="7"/>
+    <row r="819" ht="15.75" customHeight="1" s="7"/>
+    <row r="820" ht="15.75" customHeight="1" s="7"/>
+    <row r="821" ht="15.75" customHeight="1" s="7"/>
+    <row r="822" ht="15.75" customHeight="1" s="7"/>
+    <row r="823" ht="15.75" customHeight="1" s="7"/>
+    <row r="824" ht="15.75" customHeight="1" s="7"/>
+    <row r="825" ht="15.75" customHeight="1" s="7"/>
+    <row r="826" ht="15.75" customHeight="1" s="7"/>
+    <row r="827" ht="15.75" customHeight="1" s="7"/>
+    <row r="828" ht="15.75" customHeight="1" s="7"/>
+    <row r="829" ht="15.75" customHeight="1" s="7"/>
+    <row r="830" ht="15.75" customHeight="1" s="7"/>
+    <row r="831" ht="15.75" customHeight="1" s="7"/>
+    <row r="832" ht="15.75" customHeight="1" s="7"/>
+    <row r="833" ht="15.75" customHeight="1" s="7"/>
+    <row r="834" ht="15.75" customHeight="1" s="7"/>
+    <row r="835" ht="15.75" customHeight="1" s="7"/>
+    <row r="836" ht="15.75" customHeight="1" s="7"/>
+    <row r="837" ht="15.75" customHeight="1" s="7"/>
+    <row r="838" ht="15.75" customHeight="1" s="7"/>
+    <row r="839" ht="15.75" customHeight="1" s="7"/>
+    <row r="840" ht="15.75" customHeight="1" s="7"/>
+    <row r="841" ht="15.75" customHeight="1" s="7"/>
+    <row r="842" ht="15.75" customHeight="1" s="7"/>
+    <row r="843" ht="15.75" customHeight="1" s="7"/>
+    <row r="844" ht="15.75" customHeight="1" s="7"/>
+    <row r="845" ht="15.75" customHeight="1" s="7"/>
+    <row r="846" ht="15.75" customHeight="1" s="7"/>
+    <row r="847" ht="15.75" customHeight="1" s="7"/>
+    <row r="848" ht="15.75" customHeight="1" s="7"/>
+    <row r="849" ht="15.75" customHeight="1" s="7"/>
+    <row r="850" ht="15.75" customHeight="1" s="7"/>
+    <row r="851" ht="15.75" customHeight="1" s="7"/>
+    <row r="852" ht="15.75" customHeight="1" s="7"/>
+    <row r="853" ht="15.75" customHeight="1" s="7"/>
+    <row r="854" ht="15.75" customHeight="1" s="7"/>
+    <row r="855" ht="15.75" customHeight="1" s="7"/>
+    <row r="856" ht="15.75" customHeight="1" s="7"/>
+    <row r="857" ht="15.75" customHeight="1" s="7"/>
+    <row r="858" ht="15.75" customHeight="1" s="7"/>
+    <row r="859" ht="15.75" customHeight="1" s="7"/>
+    <row r="860" ht="15.75" customHeight="1" s="7"/>
+    <row r="861" ht="15.75" customHeight="1" s="7"/>
+    <row r="862" ht="15.75" customHeight="1" s="7"/>
+    <row r="863" ht="15.75" customHeight="1" s="7"/>
+    <row r="864" ht="15.75" customHeight="1" s="7"/>
+    <row r="865" ht="15.75" customHeight="1" s="7"/>
+    <row r="866" ht="15.75" customHeight="1" s="7"/>
+    <row r="867" ht="15.75" customHeight="1" s="7"/>
+    <row r="868" ht="15.75" customHeight="1" s="7"/>
+    <row r="869" ht="15.75" customHeight="1" s="7"/>
+    <row r="870" ht="15.75" customHeight="1" s="7"/>
+    <row r="871" ht="15.75" customHeight="1" s="7"/>
+    <row r="872" ht="15.75" customHeight="1" s="7"/>
+    <row r="873" ht="15.75" customHeight="1" s="7"/>
+    <row r="874" ht="15.75" customHeight="1" s="7"/>
+    <row r="875" ht="15.75" customHeight="1" s="7"/>
+    <row r="876" ht="15.75" customHeight="1" s="7"/>
+    <row r="877" ht="15.75" customHeight="1" s="7"/>
+    <row r="878" ht="15.75" customHeight="1" s="7"/>
+    <row r="879" ht="15.75" customHeight="1" s="7"/>
+    <row r="880" ht="15.75" customHeight="1" s="7"/>
+    <row r="881" ht="15.75" customHeight="1" s="7"/>
+    <row r="882" ht="15.75" customHeight="1" s="7"/>
+    <row r="883" ht="15.75" customHeight="1" s="7"/>
+    <row r="884" ht="15.75" customHeight="1" s="7"/>
+    <row r="885" ht="15.75" customHeight="1" s="7"/>
+    <row r="886" ht="15.75" customHeight="1" s="7"/>
+    <row r="887" ht="15.75" customHeight="1" s="7"/>
+    <row r="888" ht="15.75" customHeight="1" s="7"/>
+    <row r="889" ht="15.75" customHeight="1" s="7"/>
+    <row r="890" ht="15.75" customHeight="1" s="7"/>
+    <row r="891" ht="15.75" customHeight="1" s="7"/>
+    <row r="892" ht="15.75" customHeight="1" s="7"/>
+    <row r="893" ht="15.75" customHeight="1" s="7"/>
+    <row r="894" ht="15.75" customHeight="1" s="7"/>
+    <row r="895" ht="15.75" customHeight="1" s="7"/>
+    <row r="896" ht="15.75" customHeight="1" s="7"/>
+    <row r="897" ht="15.75" customHeight="1" s="7"/>
+    <row r="898" ht="15.75" customHeight="1" s="7"/>
+    <row r="899" ht="15.75" customHeight="1" s="7"/>
+    <row r="900" ht="15.75" customHeight="1" s="7"/>
+    <row r="901" ht="15.75" customHeight="1" s="7"/>
+    <row r="902" ht="15.75" customHeight="1" s="7"/>
+    <row r="903" ht="15.75" customHeight="1" s="7"/>
+    <row r="904" ht="15.75" customHeight="1" s="7"/>
+    <row r="905" ht="15.75" customHeight="1" s="7"/>
+    <row r="906" ht="15.75" customHeight="1" s="7"/>
+    <row r="907" ht="15.75" customHeight="1" s="7"/>
+    <row r="908" ht="15.75" customHeight="1" s="7"/>
+    <row r="909" ht="15.75" customHeight="1" s="7"/>
+    <row r="910" ht="15.75" customHeight="1" s="7"/>
+    <row r="911" ht="15.75" customHeight="1" s="7"/>
+    <row r="912" ht="15.75" customHeight="1" s="7"/>
+    <row r="913" ht="15.75" customHeight="1" s="7"/>
+    <row r="914" ht="15.75" customHeight="1" s="7"/>
+    <row r="915" ht="15.75" customHeight="1" s="7"/>
+    <row r="916" ht="15.75" customHeight="1" s="7"/>
+    <row r="917" ht="15.75" customHeight="1" s="7"/>
+    <row r="918" ht="15.75" customHeight="1" s="7"/>
+    <row r="919" ht="15.75" customHeight="1" s="7"/>
+    <row r="920" ht="15.75" customHeight="1" s="7"/>
+    <row r="921" ht="15.75" customHeight="1" s="7"/>
+    <row r="922" ht="15.75" customHeight="1" s="7"/>
+    <row r="923" ht="15.75" customHeight="1" s="7"/>
+    <row r="924" ht="15.75" customHeight="1" s="7"/>
+    <row r="925" ht="15.75" customHeight="1" s="7"/>
+    <row r="926" ht="15.75" customHeight="1" s="7"/>
+    <row r="927" ht="15.75" customHeight="1" s="7"/>
+    <row r="928" ht="15.75" customHeight="1" s="7"/>
+    <row r="929" ht="15.75" customHeight="1" s="7"/>
+    <row r="930" ht="15.75" customHeight="1" s="7"/>
+    <row r="931" ht="15.75" customHeight="1" s="7"/>
+    <row r="932" ht="15.75" customHeight="1" s="7"/>
+    <row r="933" ht="15.75" customHeight="1" s="7"/>
+    <row r="934" ht="15.75" customHeight="1" s="7"/>
+    <row r="935" ht="15.75" customHeight="1" s="7"/>
+    <row r="936" ht="15.75" customHeight="1" s="7"/>
+    <row r="937" ht="15.75" customHeight="1" s="7"/>
+    <row r="938" ht="15.75" customHeight="1" s="7"/>
+    <row r="939" ht="15.75" customHeight="1" s="7"/>
+    <row r="940" ht="15.75" customHeight="1" s="7"/>
+    <row r="941" ht="15.75" customHeight="1" s="7"/>
+    <row r="942" ht="15.75" customHeight="1" s="7"/>
+    <row r="943" ht="15.75" customHeight="1" s="7"/>
+    <row r="944" ht="15.75" customHeight="1" s="7"/>
+    <row r="945" ht="15.75" customHeight="1" s="7"/>
+    <row r="946" ht="15.75" customHeight="1" s="7"/>
+    <row r="947" ht="15.75" customHeight="1" s="7"/>
+    <row r="948" ht="15.75" customHeight="1" s="7"/>
+    <row r="949" ht="15.75" customHeight="1" s="7"/>
+    <row r="950" ht="15.75" customHeight="1" s="7"/>
+    <row r="951" ht="15.75" customHeight="1" s="7"/>
+    <row r="952" ht="15.75" customHeight="1" s="7"/>
+    <row r="953" ht="15.75" customHeight="1" s="7"/>
+    <row r="954" ht="15.75" customHeight="1" s="7"/>
+    <row r="955" ht="15.75" customHeight="1" s="7"/>
+    <row r="956" ht="15.75" customHeight="1" s="7"/>
+    <row r="957" ht="15.75" customHeight="1" s="7"/>
+    <row r="958" ht="15.75" customHeight="1" s="7"/>
+    <row r="959" ht="15.75" customHeight="1" s="7"/>
+    <row r="960" ht="15.75" customHeight="1" s="7"/>
+    <row r="961" ht="15.75" customHeight="1" s="7"/>
+    <row r="962" ht="15.75" customHeight="1" s="7"/>
+    <row r="963" ht="15.75" customHeight="1" s="7"/>
+    <row r="964" ht="15.75" customHeight="1" s="7"/>
+    <row r="965" ht="15.75" customHeight="1" s="7"/>
+    <row r="966" ht="15.75" customHeight="1" s="7"/>
+    <row r="967" ht="15.75" customHeight="1" s="7"/>
+    <row r="968" ht="15.75" customHeight="1" s="7"/>
+    <row r="969" ht="15.75" customHeight="1" s="7"/>
+    <row r="970" ht="15.75" customHeight="1" s="7"/>
+    <row r="971" ht="15.75" customHeight="1" s="7"/>
+    <row r="972" ht="15.75" customHeight="1" s="7"/>
+    <row r="973" ht="15.75" customHeight="1" s="7"/>
+    <row r="974" ht="15.75" customHeight="1" s="7"/>
+    <row r="975" ht="15.75" customHeight="1" s="7"/>
+    <row r="976" ht="15.75" customHeight="1" s="7"/>
+    <row r="977" ht="15.75" customHeight="1" s="7"/>
+    <row r="978" ht="15.75" customHeight="1" s="7"/>
+    <row r="979" ht="15.75" customHeight="1" s="7"/>
+    <row r="980" ht="15.75" customHeight="1" s="7"/>
+    <row r="981" ht="15.75" customHeight="1" s="7"/>
+    <row r="982" ht="15.75" customHeight="1" s="7"/>
+    <row r="983" ht="15.75" customHeight="1" s="7"/>
+    <row r="984" ht="15.75" customHeight="1" s="7"/>
+    <row r="985" ht="15.75" customHeight="1" s="7"/>
+    <row r="986" ht="15.75" customHeight="1" s="7"/>
+    <row r="987" ht="15.75" customHeight="1" s="7"/>
+    <row r="988" ht="15.75" customHeight="1" s="7"/>
+    <row r="989" ht="15.75" customHeight="1" s="7"/>
+    <row r="990" ht="15.75" customHeight="1" s="7"/>
+    <row r="991" ht="15.75" customHeight="1" s="7"/>
+    <row r="992" ht="15.75" customHeight="1" s="7"/>
+    <row r="993" ht="15.75" customHeight="1" s="7"/>
+    <row r="994" ht="15.75" customHeight="1" s="7"/>
+    <row r="995" ht="15.75" customHeight="1" s="7"/>
+    <row r="996" ht="15.75" customHeight="1" s="7"/>
+    <row r="997" ht="15.75" customHeight="1" s="7"/>
+    <row r="998" ht="15.75" customHeight="1" s="7"/>
+    <row r="999" ht="15.75" customHeight="1" s="7"/>
+    <row r="1000" ht="15.75" customHeight="1" s="7"/>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
+  <pageSetup orientation="landscape"/>
 </worksheet>
 </file>
--- a/para_equipe/nomes_dos_times.xlsx
+++ b/para_equipe/nomes_dos_times.xlsx
@@ -1895,12 +1895,12 @@
       <c r="C41" s="5" t="n"/>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>FATEC PG</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Faculdade de Tecnologia de São Paulo</t>
+          <t>Faculdade de Tecnologia de Praia Grande</t>
         </is>
       </c>
       <c r="F41" s="6" t="n">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>Faculdade Donaduzz</t>
+          <t>Faculdade Donaduzzi</t>
         </is>
       </c>
       <c r="F57" s="6" t="n">
